--- a/lisp-kernel/00devdocs/memory-layout-x86-64.xlsx
+++ b/lisp-kernel/00devdocs/memory-layout-x86-64.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/HansVanSlooten/repos/ccl/lisp-kernel/00devdocs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D640CAD7-5395-D643-8485-ABACF3101571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{943B4A94-E37E-524D-A237-2A15C0B4732D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="20980" activeTab="1" xr2:uid="{131F1BAB-D804-8246-991C-2A750BBECEE3}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="21660" activeTab="1" xr2:uid="{131F1BAB-D804-8246-991C-2A750BBECEE3}"/>
   </bookViews>
   <sheets>
     <sheet name="Memory Layout" sheetId="1" r:id="rId1"/>
-    <sheet name="Garbage Collector" sheetId="2" r:id="rId2"/>
+    <sheet name="Tags" sheetId="3" r:id="rId2"/>
+    <sheet name="Garbage Collector" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Memory Layout'!$A$1:$J$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Garbage Collector'!$A:$E</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Memory Layout'!$A$1:$I$55</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="252">
   <si>
     <t>0x308000000000</t>
   </si>
@@ -314,13 +315,496 @@
   </si>
   <si>
     <t>pmcl-kernel.c/create_reserved_area (random address from mmap)</t>
+  </si>
+  <si>
+    <t>Each 64-bit node in this maps to 64 nodes of memory (i.e. bitvector)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dynamic memory starts at 0x302000000000, so </t>
+  </si>
+  <si>
+    <t>x86-64 Tag Definitions</t>
+  </si>
+  <si>
+    <t>0x3f (63)</t>
+  </si>
+  <si>
+    <t>0x37 (55)</t>
+  </si>
+  <si>
+    <t>0x2f (47)</t>
+  </si>
+  <si>
+    <t>0x27 (39)</t>
+  </si>
+  <si>
+    <t>0x1f (31)</t>
+  </si>
+  <si>
+    <t>0x17 (23)</t>
+  </si>
+  <si>
+    <t>0x0f (15)</t>
+  </si>
+  <si>
+    <t>0x07 (7)</t>
+  </si>
+  <si>
+    <t>0x00 (0)</t>
+  </si>
+  <si>
+    <t>0x08 (8)</t>
+  </si>
+  <si>
+    <t>0x10 (16)</t>
+  </si>
+  <si>
+    <t>0x18 (24)</t>
+  </si>
+  <si>
+    <t>0x20 (32)</t>
+  </si>
+  <si>
+    <t>0x28 (40)</t>
+  </si>
+  <si>
+    <t>0x30 (48)</t>
+  </si>
+  <si>
+    <t>0x38 (56)</t>
+  </si>
+  <si>
+    <t>tag</t>
+  </si>
+  <si>
+    <t>subtag</t>
+  </si>
+  <si>
+    <t>fixnumtag</t>
+  </si>
+  <si>
+    <t>fulltag_even_fixnum</t>
+  </si>
+  <si>
+    <t>fulltag</t>
+  </si>
+  <si>
+    <t>fulltag_imm_0</t>
+  </si>
+  <si>
+    <t>fulltag_imm_1</t>
+  </si>
+  <si>
+    <t>tag_fixnum</t>
+  </si>
+  <si>
+    <t>tag_imm_0</t>
+  </si>
+  <si>
+    <t>tag_imm_1</t>
+  </si>
+  <si>
+    <t>tag_list</t>
+  </si>
+  <si>
+    <t>tag_tra</t>
+  </si>
+  <si>
+    <t>tag_misc</t>
+  </si>
+  <si>
+    <t>tag_symbol</t>
+  </si>
+  <si>
+    <t>tag_function</t>
+  </si>
+  <si>
+    <t>fulltag_cons</t>
+  </si>
+  <si>
+    <t>fulltag_tra_0</t>
+  </si>
+  <si>
+    <t>fulltag_nodeheader_0</t>
+  </si>
+  <si>
+    <t>fulltag_nodeheader_1</t>
+  </si>
+  <si>
+    <t>fulltag_odd_fixnum</t>
+  </si>
+  <si>
+    <t>fulltag_nil</t>
+  </si>
+  <si>
+    <t>fulltag_tra_1</t>
+  </si>
+  <si>
+    <t>fulltag_misc</t>
+  </si>
+  <si>
+    <t>fulltag_symbol</t>
+  </si>
+  <si>
+    <t>fulltag_function</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>0x0 (0)</t>
+  </si>
+  <si>
+    <t>0x3 (3)</t>
+  </si>
+  <si>
+    <t>0x8 (8)</t>
+  </si>
+  <si>
+    <t>0xb (11)</t>
+  </si>
+  <si>
+    <t>0x4 (4)</t>
+  </si>
+  <si>
+    <t>0xc (12)</t>
+  </si>
+  <si>
+    <t>0xd (13)</t>
+  </si>
+  <si>
+    <t>subtag_symbol</t>
+  </si>
+  <si>
+    <t>subtag_catch_frame</t>
+  </si>
+  <si>
+    <t>subtag_hash_vector</t>
+  </si>
+  <si>
+    <t>subtag_pool</t>
+  </si>
+  <si>
+    <t>subtag_weak</t>
+  </si>
+  <si>
+    <t>subtag_package</t>
+  </si>
+  <si>
+    <t>subtag_slot_vector</t>
+  </si>
+  <si>
+    <t>subtag_basic_stream</t>
+  </si>
+  <si>
+    <t>subtag_function</t>
+  </si>
+  <si>
+    <t>subtag_ratio</t>
+  </si>
+  <si>
+    <t>subtag_complex</t>
+  </si>
+  <si>
+    <t>subtag_struct</t>
+  </si>
+  <si>
+    <t>subtag_istruct</t>
+  </si>
+  <si>
+    <t>subtag_value_cell</t>
+  </si>
+  <si>
+    <t>subtag_xfunction</t>
+  </si>
+  <si>
+    <t>subtag_lock</t>
+  </si>
+  <si>
+    <t>subtag_instance</t>
+  </si>
+  <si>
+    <t>0x15 (21)</t>
+  </si>
+  <si>
+    <t>0x25 (37)</t>
+  </si>
+  <si>
+    <t>0x35 (53)</t>
+  </si>
+  <si>
+    <t>0x45 (69)</t>
+  </si>
+  <si>
+    <t>0x55 (85)</t>
+  </si>
+  <si>
+    <t>0x65 (101)</t>
+  </si>
+  <si>
+    <t>0x75 (117)</t>
+  </si>
+  <si>
+    <t>0x85 (133)</t>
+  </si>
+  <si>
+    <t>0x95 (149)</t>
+  </si>
+  <si>
+    <t>0x16 (22)</t>
+  </si>
+  <si>
+    <t>0x26 (38)</t>
+  </si>
+  <si>
+    <t>0x36 (54)</t>
+  </si>
+  <si>
+    <t>0x46 (70)</t>
+  </si>
+  <si>
+    <t>0x56 (86)</t>
+  </si>
+  <si>
+    <t>0x66 (102)</t>
+  </si>
+  <si>
+    <t>0x76 (118)</t>
+  </si>
+  <si>
+    <t>0x86 (134)</t>
+  </si>
+  <si>
+    <t>subtag_arrayH</t>
+  </si>
+  <si>
+    <t>0xa5 (165)</t>
+  </si>
+  <si>
+    <t>subtag_vectorH</t>
+  </si>
+  <si>
+    <t>subtag_simple_vector</t>
+  </si>
+  <si>
+    <t>0xa6 (166)</t>
+  </si>
+  <si>
+    <t>0xb6 (182)</t>
+  </si>
+  <si>
+    <t>subtag_complex_double_float_vector</t>
+  </si>
+  <si>
+    <t>subtag_s16_vector</t>
+  </si>
+  <si>
+    <t>subtag_u16_vector</t>
+  </si>
+  <si>
+    <t>subtag_s8_vector</t>
+  </si>
+  <si>
+    <t>subtag_u8_vector</t>
+  </si>
+  <si>
+    <t>subtag_bit_vector</t>
+  </si>
+  <si>
+    <t>min_8_bit_ivector_subtag</t>
+  </si>
+  <si>
+    <t>fulltag_immheader_0 / ivector_class_other_bit</t>
+  </si>
+  <si>
+    <t>0xa7 (167)</t>
+  </si>
+  <si>
+    <t>0x97 (151)</t>
+  </si>
+  <si>
+    <t>0xb7 (183)</t>
+  </si>
+  <si>
+    <t>0xc7 (199)</t>
+  </si>
+  <si>
+    <t>0xd7 (215)</t>
+  </si>
+  <si>
+    <t>0xe7 (231)</t>
+  </si>
+  <si>
+    <t>0xf7 (247)</t>
+  </si>
+  <si>
+    <t>fulltag_immheader_1 / ivector_class_32_bit</t>
+  </si>
+  <si>
+    <t>subtag_bignum</t>
+  </si>
+  <si>
+    <t>subtag_double_float</t>
+  </si>
+  <si>
+    <t>subtag_xcode_vector</t>
+  </si>
+  <si>
+    <t>subtag_complex_single_float</t>
+  </si>
+  <si>
+    <t>subtag_complex_double_float</t>
+  </si>
+  <si>
+    <t>subtag_simple_base_string</t>
+  </si>
+  <si>
+    <t>subtag_s32_vector</t>
+  </si>
+  <si>
+    <t>subtag_u32_vector</t>
+  </si>
+  <si>
+    <t>subtag_single_float_vector</t>
+  </si>
+  <si>
+    <t>0x09 (9)</t>
+  </si>
+  <si>
+    <t>0x19 (25)</t>
+  </si>
+  <si>
+    <t>0x29 (41)</t>
+  </si>
+  <si>
+    <t>0x39 (57)</t>
+  </si>
+  <si>
+    <t>0x49 (73)</t>
+  </si>
+  <si>
+    <t>0x59 (89)</t>
+  </si>
+  <si>
+    <t>0xc9 (201)</t>
+  </si>
+  <si>
+    <t>0xd9 (217)</t>
+  </si>
+  <si>
+    <t>0xe9 (233)</t>
+  </si>
+  <si>
+    <t>fulltag_immheader_2 / ivector_class_64_bit</t>
+  </si>
+  <si>
+    <t>subtag_fixnum_vector</t>
+  </si>
+  <si>
+    <t>subtag_s64_vector</t>
+  </si>
+  <si>
+    <t>subtag_u64_vector</t>
+  </si>
+  <si>
+    <t>subtag_double_float_vector</t>
+  </si>
+  <si>
+    <t>0xca (202)</t>
+  </si>
+  <si>
+    <t>0xda (218)</t>
+  </si>
+  <si>
+    <t>0xea (234)</t>
+  </si>
+  <si>
+    <t>0xfa (250)</t>
+  </si>
+  <si>
+    <t>0xe (14)</t>
+  </si>
+  <si>
+    <t>0xf (15)</t>
+  </si>
+  <si>
+    <t>subtag_single_float</t>
+  </si>
+  <si>
+    <t>0x01 (1)</t>
+  </si>
+  <si>
+    <t>subtag_character</t>
+  </si>
+  <si>
+    <t>0x02 (2)</t>
+  </si>
+  <si>
+    <t>subtag_unbound</t>
+  </si>
+  <si>
+    <t>subtag_slot_unbound</t>
+  </si>
+  <si>
+    <t>subtag_illegal</t>
+  </si>
+  <si>
+    <t>subtag_no_thread_local_binding</t>
+  </si>
+  <si>
+    <t>subtag_reserved_frame</t>
+  </si>
+  <si>
+    <t>subtag_forward_marker</t>
+  </si>
+  <si>
+    <t>function_boundary_marker</t>
+  </si>
+  <si>
+    <t>0x12 (18)</t>
+  </si>
+  <si>
+    <t>0x22 (34)</t>
+  </si>
+  <si>
+    <t>0x32 (50)</t>
+  </si>
+  <si>
+    <t>0x42 (66)</t>
+  </si>
+  <si>
+    <t>0x52 (82)</t>
+  </si>
+  <si>
+    <t>0x62 (98)</t>
+  </si>
+  <si>
+    <t>0xf2 (242)</t>
+  </si>
+  <si>
+    <t>61-bit Even Fixnum</t>
+  </si>
+  <si>
+    <t>61-bit Odd Fixnum</t>
+  </si>
+  <si>
+    <t>32-bit Float</t>
+  </si>
+  <si>
+    <t>Unsigned 32-bit Character</t>
+  </si>
+  <si>
+    <t>56-bit Element Count</t>
+  </si>
+  <si>
+    <t>Address of cons (dnode, 16-byte aligned)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -353,8 +837,21 @@
       <name val="Consolas"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -415,8 +912,11 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="darkUp"/>
+    </fill>
   </fills>
-  <borders count="40">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -737,15 +1237,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="dotted">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -839,31 +1330,18 @@
     </border>
     <border>
       <left/>
-      <right style="dotted">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
       <right/>
-      <top/>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -957,35 +1435,32 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="180"/>
@@ -1014,14 +1489,97 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1360,520 +1918,515 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="7"/>
     <col min="2" max="2" width="12.5" style="7" customWidth="1"/>
-    <col min="3" max="3" width="3" customWidth="1"/>
-    <col min="4" max="4" width="3.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5" style="14" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" style="10"/>
-    <col min="9" max="9" width="21.5" style="7" customWidth="1"/>
-    <col min="10" max="10" width="2.83203125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="3.33203125" style="7" customWidth="1"/>
-    <col min="12" max="12" width="18.5" style="7" customWidth="1"/>
+    <col min="3" max="3" width="11.5" style="14" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" style="10"/>
+    <col min="7" max="7" width="21.5" style="7" customWidth="1"/>
+    <col min="8" max="8" width="2.6640625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="2.83203125" style="7" customWidth="1"/>
+    <col min="10" max="10" width="3.33203125" style="7" customWidth="1"/>
+    <col min="11" max="11" width="18.5" style="7" customWidth="1"/>
+    <col min="12" max="12" width="20.5" style="14" customWidth="1"/>
+    <col min="13" max="14" width="10.83203125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="4:10" x14ac:dyDescent="0.2">
-      <c r="F2" s="8"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="4:10" x14ac:dyDescent="0.2">
-      <c r="D3" s="82" t="s">
+    <row r="1" spans="3:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="D2" s="8"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C3" s="66"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="48"/>
+      <c r="H3" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="67"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="48"/>
-      <c r="J3" s="76" t="s">
+      <c r="I3" s="73" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="4:10" x14ac:dyDescent="0.2">
-      <c r="D4" s="83"/>
-      <c r="E4" s="67" t="s">
+    <row r="4" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C4" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47" t="s">
+      <c r="D4" s="46"/>
+      <c r="E4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="48"/>
-      <c r="J4" s="77"/>
-    </row>
-    <row r="5" spans="4:10" x14ac:dyDescent="0.2">
-      <c r="D5" s="83"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="48"/>
-      <c r="J5" s="77"/>
-    </row>
-    <row r="6" spans="4:10" x14ac:dyDescent="0.2">
-      <c r="D6" s="83"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="77"/>
-    </row>
-    <row r="7" spans="4:10" x14ac:dyDescent="0.2">
-      <c r="D7" s="83"/>
-      <c r="E7" s="67" t="s">
+      <c r="F4" s="48"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="74"/>
+    </row>
+    <row r="5" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C5" s="66"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="48"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="74"/>
+    </row>
+    <row r="6" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C6" s="66"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="80"/>
+      <c r="I6" s="74"/>
+    </row>
+    <row r="7" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C7" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="19"/>
-      <c r="G7" s="20" t="s">
+      <c r="D7" s="19"/>
+      <c r="E7" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="21"/>
-      <c r="I7" s="7" t="s">
+      <c r="F7" s="21"/>
+      <c r="G7" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="J7" s="77"/>
-    </row>
-    <row r="8" spans="4:10" x14ac:dyDescent="0.2">
-      <c r="D8" s="83"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="42"/>
-      <c r="J8" s="77"/>
-    </row>
-    <row r="9" spans="4:10" x14ac:dyDescent="0.2">
-      <c r="D9" s="83"/>
-      <c r="E9" s="67" t="s">
+      <c r="H7" s="80"/>
+      <c r="I7" s="74"/>
+    </row>
+    <row r="8" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C8" s="66"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="42"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="74"/>
+    </row>
+    <row r="9" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C9" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="40"/>
-      <c r="G9" s="41" t="s">
+      <c r="D9" s="40"/>
+      <c r="E9" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="42"/>
-      <c r="J9" s="77"/>
-    </row>
-    <row r="10" spans="4:10" x14ac:dyDescent="0.2">
-      <c r="D10" s="83"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="42"/>
-      <c r="J10" s="77"/>
-    </row>
-    <row r="11" spans="4:10" x14ac:dyDescent="0.2">
-      <c r="D11" s="83"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="7" t="s">
+      <c r="F9" s="42"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="74"/>
+    </row>
+    <row r="10" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C10" s="66"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="42"/>
+      <c r="H10" s="80"/>
+      <c r="I10" s="74"/>
+    </row>
+    <row r="11" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C11" s="66"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="J11" s="77"/>
-    </row>
-    <row r="12" spans="4:10" x14ac:dyDescent="0.2">
-      <c r="D12" s="83"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="1"/>
-      <c r="H12" s="2"/>
-      <c r="J12" s="77"/>
-    </row>
-    <row r="13" spans="4:10" x14ac:dyDescent="0.2">
-      <c r="D13" s="83"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="1"/>
-      <c r="H13" s="2"/>
-      <c r="J13" s="77"/>
-    </row>
-    <row r="14" spans="4:10" x14ac:dyDescent="0.2">
-      <c r="D14" s="83"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="1"/>
-      <c r="H14" s="2"/>
-      <c r="J14" s="77"/>
-    </row>
-    <row r="15" spans="4:10" x14ac:dyDescent="0.2">
-      <c r="D15" s="83"/>
-      <c r="E15" s="67"/>
-      <c r="F15" s="1"/>
-      <c r="H15" s="2"/>
-      <c r="J15" s="77"/>
-    </row>
-    <row r="16" spans="4:10" x14ac:dyDescent="0.2">
-      <c r="D16" s="83"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="1"/>
-      <c r="H16" s="2"/>
-      <c r="J16" s="77"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="D17" s="83"/>
-      <c r="E17" s="67"/>
-      <c r="F17" s="1"/>
-      <c r="H17" s="2"/>
-      <c r="J17" s="77"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="D18" s="83"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="1"/>
-      <c r="H18" s="2"/>
-      <c r="J18" s="77"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="D19" s="83"/>
-      <c r="E19" s="67"/>
-      <c r="F19" s="1"/>
-      <c r="H19" s="2"/>
-      <c r="J19" s="77"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="D20" s="83"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="1"/>
-      <c r="H20" s="2"/>
-      <c r="J20" s="77"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="D21" s="83"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="1"/>
-      <c r="H21" s="2"/>
-      <c r="J21" s="77"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="D22" s="83"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="10" t="s">
+      <c r="H11" s="80"/>
+      <c r="I11" s="74"/>
+    </row>
+    <row r="12" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C12" s="66"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="2"/>
+      <c r="H12" s="80"/>
+      <c r="I12" s="74"/>
+    </row>
+    <row r="13" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C13" s="66"/>
+      <c r="D13" s="1"/>
+      <c r="F13" s="2"/>
+      <c r="H13" s="80"/>
+      <c r="I13" s="74"/>
+    </row>
+    <row r="14" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C14" s="66"/>
+      <c r="D14" s="1"/>
+      <c r="F14" s="2"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="74"/>
+    </row>
+    <row r="15" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C15" s="66"/>
+      <c r="D15" s="1"/>
+      <c r="F15" s="2"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="74"/>
+    </row>
+    <row r="16" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C16" s="66"/>
+      <c r="D16" s="1"/>
+      <c r="F16" s="2"/>
+      <c r="H16" s="80"/>
+      <c r="I16" s="74"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C17" s="66"/>
+      <c r="D17" s="1"/>
+      <c r="F17" s="2"/>
+      <c r="H17" s="80"/>
+      <c r="I17" s="74"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C18" s="66"/>
+      <c r="D18" s="1"/>
+      <c r="F18" s="2"/>
+      <c r="H18" s="80"/>
+      <c r="I18" s="74"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C19" s="66"/>
+      <c r="D19" s="1"/>
+      <c r="F19" s="2"/>
+      <c r="H19" s="80"/>
+      <c r="I19" s="74"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C20" s="66"/>
+      <c r="D20" s="1"/>
+      <c r="F20" s="2"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="74"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C21" s="66"/>
+      <c r="D21" s="1"/>
+      <c r="F21" s="2"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="74"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C22" s="66"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="2"/>
-      <c r="I22" s="7" t="s">
+      <c r="F22" s="2"/>
+      <c r="G22" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="77"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="D23" s="83"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="51"/>
-      <c r="J23" s="77"/>
-    </row>
-    <row r="24" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="83"/>
-      <c r="E24" s="67" t="s">
+      <c r="H22" s="80"/>
+      <c r="I22" s="74"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C23" s="66"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="51"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="74"/>
+    </row>
+    <row r="24" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="F24" s="34"/>
-      <c r="G24" s="35" t="s">
+      <c r="D24" s="34"/>
+      <c r="E24" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="H24" s="36"/>
-      <c r="J24" s="77"/>
-    </row>
-    <row r="25" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F24" s="36"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="74"/>
+    </row>
+    <row r="25" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="64"/>
-      <c r="C25" s="71"/>
-      <c r="D25" s="83"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="7" t="s">
+      <c r="B25" s="63"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J25" s="78"/>
-    </row>
-    <row r="26" spans="1:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="H25" s="80"/>
+      <c r="I25" s="75"/>
+    </row>
+    <row r="26" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="65"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="83"/>
-      <c r="E26" s="67" t="s">
+      <c r="B26" s="64"/>
+      <c r="C26" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="F26" s="52"/>
-      <c r="G26" s="53" t="s">
+      <c r="D26" s="52"/>
+      <c r="E26" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="54"/>
-      <c r="J26" s="73" t="s">
+      <c r="F26" s="54"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="70" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="65"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="83"/>
-      <c r="E27" s="67"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="10" t="s">
+      <c r="B27" s="64"/>
+      <c r="C27" s="66"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H27" s="2"/>
-      <c r="J27" s="74"/>
-    </row>
-    <row r="28" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F27" s="2"/>
+      <c r="H27" s="80"/>
+      <c r="I27" s="71"/>
+    </row>
+    <row r="28" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="66"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="83"/>
-      <c r="E28" s="67"/>
-      <c r="F28" s="1"/>
-      <c r="H28" s="2"/>
-      <c r="J28" s="74"/>
-    </row>
-    <row r="29" spans="1:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="D29" s="83"/>
-      <c r="E29" s="67"/>
-      <c r="F29" s="1"/>
-      <c r="H29" s="2"/>
-      <c r="J29" s="74"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="D30" s="83"/>
-      <c r="E30" s="67"/>
-      <c r="F30" s="1"/>
-      <c r="H30" s="2"/>
-      <c r="J30" s="74"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="D31" s="83"/>
-      <c r="E31" s="67"/>
-      <c r="F31" s="1"/>
-      <c r="H31" s="2"/>
-      <c r="J31" s="74"/>
-      <c r="K31" s="79" t="s">
+      <c r="B28" s="65"/>
+      <c r="C28" s="66"/>
+      <c r="D28" s="1"/>
+      <c r="F28" s="2"/>
+      <c r="H28" s="80"/>
+      <c r="I28" s="71"/>
+    </row>
+    <row r="29" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="C29" s="66"/>
+      <c r="D29" s="1"/>
+      <c r="F29" s="2"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="71"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C30" s="66"/>
+      <c r="D30" s="1"/>
+      <c r="F30" s="2"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="71"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C31" s="66"/>
+      <c r="D31" s="1"/>
+      <c r="F31" s="2"/>
+      <c r="H31" s="80"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="76" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="D32" s="83"/>
-      <c r="E32" s="67"/>
-      <c r="F32" s="1"/>
-      <c r="H32" s="2"/>
-      <c r="J32" s="74"/>
-      <c r="K32" s="80"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="D33" s="83"/>
-      <c r="E33" s="67"/>
-      <c r="F33" s="1"/>
-      <c r="H33" s="2"/>
-      <c r="J33" s="74"/>
-      <c r="K33" s="80"/>
-      <c r="L33" s="72" t="s">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C32" s="66"/>
+      <c r="D32" s="1"/>
+      <c r="F32" s="2"/>
+      <c r="H32" s="80"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="77"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C33" s="66"/>
+      <c r="D33" s="1"/>
+      <c r="F33" s="2"/>
+      <c r="H33" s="80"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="77"/>
+      <c r="K33" s="69" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D34" s="83"/>
-      <c r="E34" s="67"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="10" t="s">
+    <row r="34" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="66"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H34" s="2"/>
-      <c r="I34" s="7" t="s">
+      <c r="F34" s="2"/>
+      <c r="G34" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J34" s="74"/>
-      <c r="K34" s="80"/>
-    </row>
-    <row r="35" spans="1:12" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H34" s="80"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="77"/>
+    </row>
+    <row r="35" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="70"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="83"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="59"/>
-      <c r="G35" s="60" t="s">
+      <c r="B35" s="68"/>
+      <c r="C35" s="67"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="H35" s="61"/>
-      <c r="I35" s="7" t="s">
+      <c r="F35" s="60"/>
+      <c r="G35" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="J35" s="74"/>
-      <c r="K35" s="81"/>
-    </row>
-    <row r="36" spans="1:12" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="D36" s="83"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="30"/>
-      <c r="J36" s="74"/>
-    </row>
-    <row r="37" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="83"/>
-      <c r="E37" s="67" t="s">
+      <c r="H35" s="80"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="78"/>
+    </row>
+    <row r="36" spans="1:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="C36" s="66"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="30"/>
+      <c r="H36" s="80"/>
+      <c r="I36" s="71"/>
+    </row>
+    <row r="37" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="F37" s="28"/>
-      <c r="G37" s="29" t="s">
+      <c r="D37" s="28"/>
+      <c r="E37" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="H37" s="30"/>
-      <c r="J37" s="74"/>
-    </row>
-    <row r="38" spans="1:12" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F37" s="30"/>
+      <c r="H37" s="80"/>
+      <c r="I37" s="71"/>
+    </row>
+    <row r="38" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="64"/>
-      <c r="C38" s="68"/>
-      <c r="D38" s="84"/>
-      <c r="E38" s="69"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="7" t="s">
+      <c r="B38" s="63"/>
+      <c r="C38" s="67"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="J38" s="75"/>
-    </row>
-    <row r="39" spans="1:12" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="H38" s="81"/>
+      <c r="I38" s="72"/>
+    </row>
+    <row r="39" spans="1:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="65"/>
-      <c r="F39" s="1"/>
-      <c r="H39" s="2"/>
-    </row>
-    <row r="40" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="64"/>
+      <c r="D39" s="1"/>
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="66"/>
-      <c r="F40" s="1"/>
-      <c r="H40" s="2"/>
-    </row>
-    <row r="41" spans="1:12" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="F41" s="1"/>
-      <c r="H41" s="2"/>
-    </row>
-    <row r="42" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="F42" s="3"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="4"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G43" s="15"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G44" s="15"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G45" s="15"/>
-    </row>
-    <row r="46" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G46" s="15"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F47" s="5"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="7" t="s">
+      <c r="B40" s="65"/>
+      <c r="D40" s="1"/>
+      <c r="F40" s="2"/>
+    </row>
+    <row r="41" spans="1:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="D41" s="1"/>
+      <c r="F41" s="2"/>
+    </row>
+    <row r="42" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D42" s="3"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E43" s="15"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E44" s="15"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E45" s="15"/>
+    </row>
+    <row r="46" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E46" s="15"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="D47" s="5"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E48" s="14" t="s">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C48" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F48" s="25"/>
-      <c r="G48" s="26" t="s">
+      <c r="D48" s="25"/>
+      <c r="E48" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="H48" s="27"/>
-      <c r="I48" s="7" t="s">
+      <c r="F48" s="27"/>
+      <c r="G48" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="5:9" x14ac:dyDescent="0.2">
-      <c r="E49" s="14" t="s">
+    <row r="49" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C49" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="F49" s="22"/>
-      <c r="G49" s="23" t="s">
+      <c r="D49" s="22"/>
+      <c r="E49" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="H49" s="24"/>
-      <c r="I49" s="7" t="s">
+      <c r="F49" s="24"/>
+      <c r="G49" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="5:9" x14ac:dyDescent="0.2">
-      <c r="E50" s="14" t="s">
+    <row r="50" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C50" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F50" s="19"/>
-      <c r="G50" s="20" t="s">
+      <c r="D50" s="19"/>
+      <c r="E50" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H50" s="21"/>
-      <c r="I50" s="7" t="s">
+      <c r="F50" s="21"/>
+      <c r="G50" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="5:9" x14ac:dyDescent="0.2">
-      <c r="E51" s="14" t="s">
+    <row r="51" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C51" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="F51" s="16"/>
-      <c r="G51" s="17" t="s">
+      <c r="D51" s="16"/>
+      <c r="E51" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H51" s="18"/>
-      <c r="I51" s="7" t="s">
+      <c r="F51" s="18"/>
+      <c r="G51" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="5:9" x14ac:dyDescent="0.2">
-      <c r="F52" s="1"/>
-      <c r="H52" s="2"/>
-    </row>
-    <row r="53" spans="5:9" x14ac:dyDescent="0.2">
-      <c r="F53" s="1"/>
-      <c r="H53" s="2"/>
-    </row>
-    <row r="54" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="F54" s="3"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="4"/>
+    <row r="52" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="D52" s="1"/>
+      <c r="F52" s="2"/>
+    </row>
+    <row r="53" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="D53" s="1"/>
+      <c r="F53" s="2"/>
+    </row>
+    <row r="54" spans="3:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D54" s="3"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="J26:J38"/>
-    <mergeCell ref="J3:J25"/>
-    <mergeCell ref="K31:K35"/>
-    <mergeCell ref="D3:D38"/>
+    <mergeCell ref="I26:I38"/>
+    <mergeCell ref="I3:I25"/>
+    <mergeCell ref="J31:J35"/>
+    <mergeCell ref="H3:H38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -1881,7 +2434,4181 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2953E451-B441-254C-8397-DF7E4B70883A}">
+  <dimension ref="B1:BS65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="2.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="55" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.83203125" style="97" customWidth="1"/>
+    <col min="6" max="12" width="2.83203125" style="10" customWidth="1"/>
+    <col min="13" max="13" width="2.83203125" style="97" customWidth="1"/>
+    <col min="14" max="20" width="2.83203125" style="10" customWidth="1"/>
+    <col min="21" max="21" width="2.83203125" style="97" customWidth="1"/>
+    <col min="22" max="28" width="2.83203125" style="10" customWidth="1"/>
+    <col min="29" max="29" width="2.83203125" style="97" customWidth="1"/>
+    <col min="30" max="35" width="2.83203125" style="10" customWidth="1"/>
+    <col min="36" max="36" width="2.83203125" style="10"/>
+    <col min="37" max="37" width="2.83203125" style="97" customWidth="1"/>
+    <col min="38" max="44" width="2.83203125" style="10"/>
+    <col min="45" max="45" width="2.83203125" style="97" customWidth="1"/>
+    <col min="46" max="52" width="2.83203125" style="10"/>
+    <col min="53" max="53" width="2.83203125" style="97" customWidth="1"/>
+    <col min="54" max="60" width="2.83203125" style="10"/>
+    <col min="61" max="61" width="2.83203125" style="97" customWidth="1"/>
+    <col min="62" max="67" width="2.83203125" style="10"/>
+    <col min="68" max="68" width="2.83203125" style="10" customWidth="1"/>
+    <col min="69" max="69" width="2.83203125" style="85"/>
+    <col min="70" max="16384" width="2.83203125" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:71" x14ac:dyDescent="0.2">
+      <c r="E1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="AC1" s="10"/>
+      <c r="AK1" s="10"/>
+      <c r="AS1" s="10"/>
+      <c r="BA1" s="10"/>
+      <c r="BI1" s="10"/>
+      <c r="BQ1" s="7"/>
+    </row>
+    <row r="2" spans="2:71" ht="28" x14ac:dyDescent="0.35">
+      <c r="B2" s="82" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="AC2" s="10"/>
+      <c r="AK2" s="10"/>
+      <c r="AS2" s="10"/>
+      <c r="BA2" s="10"/>
+      <c r="BI2" s="10"/>
+      <c r="BQ2" s="7"/>
+    </row>
+    <row r="3" spans="2:71" x14ac:dyDescent="0.2">
+      <c r="E3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="AC3" s="10"/>
+      <c r="AK3" s="10"/>
+      <c r="AS3" s="10"/>
+      <c r="BA3" s="10"/>
+      <c r="BI3" s="89" t="s">
+        <v>111</v>
+      </c>
+      <c r="BJ3" s="90"/>
+      <c r="BK3" s="90"/>
+      <c r="BL3" s="90"/>
+      <c r="BM3" s="90"/>
+      <c r="BN3" s="90"/>
+      <c r="BO3" s="90"/>
+      <c r="BP3" s="91"/>
+      <c r="BQ3" s="7"/>
+    </row>
+    <row r="4" spans="2:71" x14ac:dyDescent="0.2">
+      <c r="E4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="AC4" s="10"/>
+      <c r="AK4" s="10"/>
+      <c r="AS4" s="10"/>
+      <c r="BA4" s="10"/>
+      <c r="BI4" s="10"/>
+      <c r="BM4" s="89" t="s">
+        <v>114</v>
+      </c>
+      <c r="BN4" s="90"/>
+      <c r="BO4" s="90"/>
+      <c r="BP4" s="91"/>
+      <c r="BQ4" s="7"/>
+    </row>
+    <row r="5" spans="2:71" x14ac:dyDescent="0.2">
+      <c r="E5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="AC5" s="10"/>
+      <c r="AK5" s="10"/>
+      <c r="AS5" s="10"/>
+      <c r="BA5" s="10"/>
+      <c r="BI5" s="10"/>
+      <c r="BM5" s="93"/>
+      <c r="BN5" s="89" t="s">
+        <v>110</v>
+      </c>
+      <c r="BO5" s="90"/>
+      <c r="BP5" s="91"/>
+      <c r="BQ5" s="7"/>
+    </row>
+    <row r="6" spans="2:71" x14ac:dyDescent="0.2">
+      <c r="E6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="AC6" s="10"/>
+      <c r="AK6" s="10"/>
+      <c r="AS6" s="10"/>
+      <c r="BA6" s="10"/>
+      <c r="BI6" s="10"/>
+      <c r="BO6" s="95" t="s">
+        <v>112</v>
+      </c>
+      <c r="BP6" s="96"/>
+      <c r="BQ6" s="92"/>
+      <c r="BR6" s="92"/>
+      <c r="BS6" s="92"/>
+    </row>
+    <row r="7" spans="2:71" s="84" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="94" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="94" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="94" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="87" t="s">
+        <v>94</v>
+      </c>
+      <c r="F7" s="86"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="86"/>
+      <c r="J7" s="86"/>
+      <c r="K7" s="86"/>
+      <c r="L7" s="86" t="s">
+        <v>109</v>
+      </c>
+      <c r="M7" s="87" t="s">
+        <v>95</v>
+      </c>
+      <c r="N7" s="86"/>
+      <c r="O7" s="86"/>
+      <c r="P7" s="86"/>
+      <c r="Q7" s="86"/>
+      <c r="R7" s="86"/>
+      <c r="S7" s="86"/>
+      <c r="T7" s="86" t="s">
+        <v>108</v>
+      </c>
+      <c r="U7" s="87" t="s">
+        <v>96</v>
+      </c>
+      <c r="V7" s="86"/>
+      <c r="W7" s="86"/>
+      <c r="X7" s="86"/>
+      <c r="Y7" s="86"/>
+      <c r="Z7" s="86"/>
+      <c r="AA7" s="86"/>
+      <c r="AB7" s="86" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC7" s="87" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD7" s="86"/>
+      <c r="AE7" s="86"/>
+      <c r="AF7" s="86"/>
+      <c r="AG7" s="86"/>
+      <c r="AH7" s="86"/>
+      <c r="AI7" s="86"/>
+      <c r="AJ7" s="86" t="s">
+        <v>106</v>
+      </c>
+      <c r="AK7" s="87" t="s">
+        <v>98</v>
+      </c>
+      <c r="AL7" s="86"/>
+      <c r="AM7" s="86"/>
+      <c r="AN7" s="86"/>
+      <c r="AO7" s="86"/>
+      <c r="AP7" s="86"/>
+      <c r="AQ7" s="86"/>
+      <c r="AR7" s="86" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS7" s="87" t="s">
+        <v>99</v>
+      </c>
+      <c r="AT7" s="86"/>
+      <c r="AU7" s="86"/>
+      <c r="AV7" s="86"/>
+      <c r="AW7" s="86"/>
+      <c r="AX7" s="86"/>
+      <c r="AY7" s="86"/>
+      <c r="AZ7" s="86" t="s">
+        <v>104</v>
+      </c>
+      <c r="BA7" s="87" t="s">
+        <v>100</v>
+      </c>
+      <c r="BB7" s="86"/>
+      <c r="BC7" s="86"/>
+      <c r="BD7" s="86"/>
+      <c r="BE7" s="86"/>
+      <c r="BF7" s="86"/>
+      <c r="BG7" s="86"/>
+      <c r="BH7" s="86" t="s">
+        <v>103</v>
+      </c>
+      <c r="BI7" s="87" t="s">
+        <v>101</v>
+      </c>
+      <c r="BJ7" s="86"/>
+      <c r="BK7" s="86"/>
+      <c r="BL7" s="86"/>
+      <c r="BM7" s="86"/>
+      <c r="BN7" s="86"/>
+      <c r="BO7" s="86"/>
+      <c r="BP7" s="88" t="s">
+        <v>102</v>
+      </c>
+      <c r="BQ7" s="83"/>
+    </row>
+    <row r="8" spans="2:71" x14ac:dyDescent="0.2">
+      <c r="B8" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E8" s="89" t="s">
+        <v>246</v>
+      </c>
+      <c r="F8" s="90"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="90"/>
+      <c r="J8" s="90"/>
+      <c r="K8" s="90"/>
+      <c r="L8" s="90"/>
+      <c r="M8" s="90"/>
+      <c r="N8" s="90"/>
+      <c r="O8" s="90"/>
+      <c r="P8" s="90"/>
+      <c r="Q8" s="90"/>
+      <c r="R8" s="90"/>
+      <c r="S8" s="90"/>
+      <c r="T8" s="90"/>
+      <c r="U8" s="90"/>
+      <c r="V8" s="90"/>
+      <c r="W8" s="90"/>
+      <c r="X8" s="90"/>
+      <c r="Y8" s="90"/>
+      <c r="Z8" s="90"/>
+      <c r="AA8" s="90"/>
+      <c r="AB8" s="90"/>
+      <c r="AC8" s="90"/>
+      <c r="AD8" s="90"/>
+      <c r="AE8" s="90"/>
+      <c r="AF8" s="90"/>
+      <c r="AG8" s="90"/>
+      <c r="AH8" s="90"/>
+      <c r="AI8" s="90"/>
+      <c r="AJ8" s="90"/>
+      <c r="AK8" s="90"/>
+      <c r="AL8" s="90"/>
+      <c r="AM8" s="90"/>
+      <c r="AN8" s="90"/>
+      <c r="AO8" s="90"/>
+      <c r="AP8" s="90"/>
+      <c r="AQ8" s="90"/>
+      <c r="AR8" s="90"/>
+      <c r="AS8" s="90"/>
+      <c r="AT8" s="90"/>
+      <c r="AU8" s="90"/>
+      <c r="AV8" s="90"/>
+      <c r="AW8" s="90"/>
+      <c r="AX8" s="90"/>
+      <c r="AY8" s="90"/>
+      <c r="AZ8" s="90"/>
+      <c r="BA8" s="90"/>
+      <c r="BB8" s="90"/>
+      <c r="BC8" s="90"/>
+      <c r="BD8" s="90"/>
+      <c r="BE8" s="90"/>
+      <c r="BF8" s="90"/>
+      <c r="BG8" s="90"/>
+      <c r="BH8" s="90"/>
+      <c r="BI8" s="90"/>
+      <c r="BJ8" s="90"/>
+      <c r="BK8" s="90"/>
+      <c r="BL8" s="91"/>
+      <c r="BM8" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN8" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO8" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP8" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR8" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="2:71" x14ac:dyDescent="0.2">
+      <c r="B9" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="E9" s="89" t="s">
+        <v>248</v>
+      </c>
+      <c r="F9" s="90"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="90"/>
+      <c r="I9" s="90"/>
+      <c r="J9" s="90"/>
+      <c r="K9" s="90"/>
+      <c r="L9" s="90"/>
+      <c r="M9" s="90"/>
+      <c r="N9" s="90"/>
+      <c r="O9" s="90"/>
+      <c r="P9" s="90"/>
+      <c r="Q9" s="90"/>
+      <c r="R9" s="90"/>
+      <c r="S9" s="90"/>
+      <c r="T9" s="90"/>
+      <c r="U9" s="90"/>
+      <c r="V9" s="90"/>
+      <c r="W9" s="90"/>
+      <c r="X9" s="90"/>
+      <c r="Y9" s="90"/>
+      <c r="Z9" s="90"/>
+      <c r="AA9" s="90"/>
+      <c r="AB9" s="90"/>
+      <c r="AC9" s="98"/>
+      <c r="AD9" s="98"/>
+      <c r="AE9" s="98"/>
+      <c r="AF9" s="98"/>
+      <c r="AG9" s="98"/>
+      <c r="AH9" s="98"/>
+      <c r="AI9" s="98"/>
+      <c r="AJ9" s="99"/>
+      <c r="AK9" s="100"/>
+      <c r="AL9" s="101"/>
+      <c r="AM9" s="101"/>
+      <c r="AN9" s="101"/>
+      <c r="AO9" s="101"/>
+      <c r="AP9" s="101"/>
+      <c r="AQ9" s="101"/>
+      <c r="AR9" s="101"/>
+      <c r="AS9" s="100"/>
+      <c r="AT9" s="101"/>
+      <c r="AU9" s="101"/>
+      <c r="AV9" s="101"/>
+      <c r="AW9" s="101"/>
+      <c r="AX9" s="101"/>
+      <c r="AY9" s="101"/>
+      <c r="AZ9" s="101"/>
+      <c r="BA9" s="100"/>
+      <c r="BB9" s="101"/>
+      <c r="BC9" s="101"/>
+      <c r="BD9" s="101"/>
+      <c r="BE9" s="101"/>
+      <c r="BF9" s="101"/>
+      <c r="BG9" s="101"/>
+      <c r="BH9" s="101"/>
+      <c r="BI9" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ9" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK9" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL9" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM9" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN9" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO9" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP9" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR9" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="10" spans="2:71" x14ac:dyDescent="0.2">
+      <c r="B10" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E10" s="100"/>
+      <c r="F10" s="101"/>
+      <c r="G10" s="101"/>
+      <c r="H10" s="101"/>
+      <c r="I10" s="101"/>
+      <c r="J10" s="101"/>
+      <c r="K10" s="101"/>
+      <c r="L10" s="101"/>
+      <c r="M10" s="100"/>
+      <c r="N10" s="101"/>
+      <c r="O10" s="101"/>
+      <c r="P10" s="101"/>
+      <c r="Q10" s="101"/>
+      <c r="R10" s="101"/>
+      <c r="S10" s="101"/>
+      <c r="T10" s="101"/>
+      <c r="U10" s="100"/>
+      <c r="V10" s="101"/>
+      <c r="W10" s="101"/>
+      <c r="X10" s="101"/>
+      <c r="Y10" s="101"/>
+      <c r="Z10" s="101"/>
+      <c r="AA10" s="101"/>
+      <c r="AB10" s="101"/>
+      <c r="AC10" s="89" t="s">
+        <v>249</v>
+      </c>
+      <c r="AD10" s="90"/>
+      <c r="AE10" s="90"/>
+      <c r="AF10" s="90"/>
+      <c r="AG10" s="90"/>
+      <c r="AH10" s="90"/>
+      <c r="AI10" s="90"/>
+      <c r="AJ10" s="90"/>
+      <c r="AK10" s="90"/>
+      <c r="AL10" s="90"/>
+      <c r="AM10" s="90"/>
+      <c r="AN10" s="90"/>
+      <c r="AO10" s="90"/>
+      <c r="AP10" s="90"/>
+      <c r="AQ10" s="90"/>
+      <c r="AR10" s="90"/>
+      <c r="AS10" s="90"/>
+      <c r="AT10" s="90"/>
+      <c r="AU10" s="90"/>
+      <c r="AV10" s="90"/>
+      <c r="AW10" s="90"/>
+      <c r="AX10" s="90"/>
+      <c r="AY10" s="90"/>
+      <c r="AZ10" s="90"/>
+      <c r="BA10" s="90"/>
+      <c r="BB10" s="90"/>
+      <c r="BC10" s="90"/>
+      <c r="BD10" s="90"/>
+      <c r="BE10" s="90"/>
+      <c r="BF10" s="90"/>
+      <c r="BG10" s="90"/>
+      <c r="BH10" s="91"/>
+      <c r="BI10" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ10" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK10" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL10" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM10" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN10" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO10" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP10" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR10" s="7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="11" spans="2:71" x14ac:dyDescent="0.2">
+      <c r="B11" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="E11" s="100"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="101"/>
+      <c r="I11" s="101"/>
+      <c r="J11" s="101"/>
+      <c r="K11" s="101"/>
+      <c r="L11" s="101"/>
+      <c r="M11" s="100"/>
+      <c r="N11" s="101"/>
+      <c r="O11" s="101"/>
+      <c r="P11" s="101"/>
+      <c r="Q11" s="101"/>
+      <c r="R11" s="101"/>
+      <c r="S11" s="101"/>
+      <c r="T11" s="101"/>
+      <c r="U11" s="100"/>
+      <c r="V11" s="101"/>
+      <c r="W11" s="101"/>
+      <c r="X11" s="101"/>
+      <c r="Y11" s="101"/>
+      <c r="Z11" s="101"/>
+      <c r="AA11" s="101"/>
+      <c r="AB11" s="101"/>
+      <c r="AC11" s="100"/>
+      <c r="AD11" s="101"/>
+      <c r="AE11" s="101"/>
+      <c r="AF11" s="101"/>
+      <c r="AG11" s="101"/>
+      <c r="AH11" s="101"/>
+      <c r="AI11" s="101"/>
+      <c r="AJ11" s="101"/>
+      <c r="AK11" s="100"/>
+      <c r="AL11" s="101"/>
+      <c r="AM11" s="101"/>
+      <c r="AN11" s="101"/>
+      <c r="AO11" s="101"/>
+      <c r="AP11" s="101"/>
+      <c r="AQ11" s="101"/>
+      <c r="AR11" s="101"/>
+      <c r="AS11" s="100"/>
+      <c r="AT11" s="101"/>
+      <c r="AU11" s="101"/>
+      <c r="AV11" s="101"/>
+      <c r="AW11" s="101"/>
+      <c r="AX11" s="101"/>
+      <c r="AY11" s="101"/>
+      <c r="AZ11" s="101"/>
+      <c r="BA11" s="100"/>
+      <c r="BB11" s="101"/>
+      <c r="BC11" s="101"/>
+      <c r="BD11" s="101"/>
+      <c r="BE11" s="101"/>
+      <c r="BF11" s="101"/>
+      <c r="BG11" s="101"/>
+      <c r="BH11" s="101"/>
+      <c r="BI11" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ11" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK11" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL11" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM11" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN11" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO11" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP11" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR11" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="12" spans="2:71" x14ac:dyDescent="0.2">
+      <c r="B12" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="E12" s="100"/>
+      <c r="F12" s="101"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="101"/>
+      <c r="I12" s="101"/>
+      <c r="J12" s="101"/>
+      <c r="K12" s="101"/>
+      <c r="L12" s="101"/>
+      <c r="M12" s="100"/>
+      <c r="N12" s="101"/>
+      <c r="O12" s="101"/>
+      <c r="P12" s="101"/>
+      <c r="Q12" s="101"/>
+      <c r="R12" s="101"/>
+      <c r="S12" s="101"/>
+      <c r="T12" s="101"/>
+      <c r="U12" s="100"/>
+      <c r="V12" s="101"/>
+      <c r="W12" s="101"/>
+      <c r="X12" s="101"/>
+      <c r="Y12" s="101"/>
+      <c r="Z12" s="101"/>
+      <c r="AA12" s="101"/>
+      <c r="AB12" s="101"/>
+      <c r="AC12" s="100"/>
+      <c r="AD12" s="101"/>
+      <c r="AE12" s="101"/>
+      <c r="AF12" s="101"/>
+      <c r="AG12" s="101"/>
+      <c r="AH12" s="101"/>
+      <c r="AI12" s="101"/>
+      <c r="AJ12" s="101"/>
+      <c r="AK12" s="100"/>
+      <c r="AL12" s="101"/>
+      <c r="AM12" s="101"/>
+      <c r="AN12" s="101"/>
+      <c r="AO12" s="101"/>
+      <c r="AP12" s="101"/>
+      <c r="AQ12" s="101"/>
+      <c r="AR12" s="101"/>
+      <c r="AS12" s="100"/>
+      <c r="AT12" s="101"/>
+      <c r="AU12" s="101"/>
+      <c r="AV12" s="101"/>
+      <c r="AW12" s="101"/>
+      <c r="AX12" s="101"/>
+      <c r="AY12" s="101"/>
+      <c r="AZ12" s="101"/>
+      <c r="BA12" s="100"/>
+      <c r="BB12" s="101"/>
+      <c r="BC12" s="101"/>
+      <c r="BD12" s="101"/>
+      <c r="BE12" s="101"/>
+      <c r="BF12" s="101"/>
+      <c r="BG12" s="101"/>
+      <c r="BH12" s="101"/>
+      <c r="BI12" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ12" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK12" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL12" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM12" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN12" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO12" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP12" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR12" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" spans="2:71" x14ac:dyDescent="0.2">
+      <c r="B13" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="E13" s="100"/>
+      <c r="F13" s="101"/>
+      <c r="G13" s="101"/>
+      <c r="H13" s="101"/>
+      <c r="I13" s="101"/>
+      <c r="J13" s="101"/>
+      <c r="K13" s="101"/>
+      <c r="L13" s="101"/>
+      <c r="M13" s="100"/>
+      <c r="N13" s="101"/>
+      <c r="O13" s="101"/>
+      <c r="P13" s="101"/>
+      <c r="Q13" s="101"/>
+      <c r="R13" s="101"/>
+      <c r="S13" s="101"/>
+      <c r="T13" s="101"/>
+      <c r="U13" s="100"/>
+      <c r="V13" s="101"/>
+      <c r="W13" s="101"/>
+      <c r="X13" s="101"/>
+      <c r="Y13" s="101"/>
+      <c r="Z13" s="101"/>
+      <c r="AA13" s="101"/>
+      <c r="AB13" s="101"/>
+      <c r="AC13" s="100"/>
+      <c r="AD13" s="101"/>
+      <c r="AE13" s="101"/>
+      <c r="AF13" s="101"/>
+      <c r="AG13" s="101"/>
+      <c r="AH13" s="101"/>
+      <c r="AI13" s="101"/>
+      <c r="AJ13" s="101"/>
+      <c r="AK13" s="100"/>
+      <c r="AL13" s="101"/>
+      <c r="AM13" s="101"/>
+      <c r="AN13" s="101"/>
+      <c r="AO13" s="101"/>
+      <c r="AP13" s="101"/>
+      <c r="AQ13" s="101"/>
+      <c r="AR13" s="101"/>
+      <c r="AS13" s="100"/>
+      <c r="AT13" s="101"/>
+      <c r="AU13" s="101"/>
+      <c r="AV13" s="101"/>
+      <c r="AW13" s="101"/>
+      <c r="AX13" s="101"/>
+      <c r="AY13" s="101"/>
+      <c r="AZ13" s="101"/>
+      <c r="BA13" s="100"/>
+      <c r="BB13" s="101"/>
+      <c r="BC13" s="101"/>
+      <c r="BD13" s="101"/>
+      <c r="BE13" s="101"/>
+      <c r="BF13" s="101"/>
+      <c r="BG13" s="101"/>
+      <c r="BH13" s="101"/>
+      <c r="BI13" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ13" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK13" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL13" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM13" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN13" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO13" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP13" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR13" s="7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="14" spans="2:71" x14ac:dyDescent="0.2">
+      <c r="B14" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="E14" s="100"/>
+      <c r="F14" s="101"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="101"/>
+      <c r="I14" s="101"/>
+      <c r="J14" s="101"/>
+      <c r="K14" s="101"/>
+      <c r="L14" s="101"/>
+      <c r="M14" s="100"/>
+      <c r="N14" s="101"/>
+      <c r="O14" s="101"/>
+      <c r="P14" s="101"/>
+      <c r="Q14" s="101"/>
+      <c r="R14" s="101"/>
+      <c r="S14" s="101"/>
+      <c r="T14" s="101"/>
+      <c r="U14" s="100"/>
+      <c r="V14" s="101"/>
+      <c r="W14" s="101"/>
+      <c r="X14" s="101"/>
+      <c r="Y14" s="101"/>
+      <c r="Z14" s="101"/>
+      <c r="AA14" s="101"/>
+      <c r="AB14" s="101"/>
+      <c r="AC14" s="100"/>
+      <c r="AD14" s="101"/>
+      <c r="AE14" s="101"/>
+      <c r="AF14" s="101"/>
+      <c r="AG14" s="101"/>
+      <c r="AH14" s="101"/>
+      <c r="AI14" s="101"/>
+      <c r="AJ14" s="101"/>
+      <c r="AK14" s="100"/>
+      <c r="AL14" s="101"/>
+      <c r="AM14" s="101"/>
+      <c r="AN14" s="101"/>
+      <c r="AO14" s="101"/>
+      <c r="AP14" s="101"/>
+      <c r="AQ14" s="101"/>
+      <c r="AR14" s="101"/>
+      <c r="AS14" s="100"/>
+      <c r="AT14" s="101"/>
+      <c r="AU14" s="101"/>
+      <c r="AV14" s="101"/>
+      <c r="AW14" s="101"/>
+      <c r="AX14" s="101"/>
+      <c r="AY14" s="101"/>
+      <c r="AZ14" s="101"/>
+      <c r="BA14" s="100"/>
+      <c r="BB14" s="101"/>
+      <c r="BC14" s="101"/>
+      <c r="BD14" s="101"/>
+      <c r="BE14" s="101"/>
+      <c r="BF14" s="101"/>
+      <c r="BG14" s="101"/>
+      <c r="BH14" s="101"/>
+      <c r="BI14" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ14" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK14" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL14" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM14" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN14" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO14" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP14" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR14" s="7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="15" spans="2:71" x14ac:dyDescent="0.2">
+      <c r="B15" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="E15" s="100"/>
+      <c r="F15" s="101"/>
+      <c r="G15" s="101"/>
+      <c r="H15" s="101"/>
+      <c r="I15" s="101"/>
+      <c r="J15" s="101"/>
+      <c r="K15" s="101"/>
+      <c r="L15" s="101"/>
+      <c r="M15" s="100"/>
+      <c r="N15" s="101"/>
+      <c r="O15" s="101"/>
+      <c r="P15" s="101"/>
+      <c r="Q15" s="101"/>
+      <c r="R15" s="101"/>
+      <c r="S15" s="101"/>
+      <c r="T15" s="101"/>
+      <c r="U15" s="100"/>
+      <c r="V15" s="101"/>
+      <c r="W15" s="101"/>
+      <c r="X15" s="101"/>
+      <c r="Y15" s="101"/>
+      <c r="Z15" s="101"/>
+      <c r="AA15" s="101"/>
+      <c r="AB15" s="101"/>
+      <c r="AC15" s="100"/>
+      <c r="AD15" s="101"/>
+      <c r="AE15" s="101"/>
+      <c r="AF15" s="101"/>
+      <c r="AG15" s="101"/>
+      <c r="AH15" s="101"/>
+      <c r="AI15" s="101"/>
+      <c r="AJ15" s="101"/>
+      <c r="AK15" s="100"/>
+      <c r="AL15" s="101"/>
+      <c r="AM15" s="101"/>
+      <c r="AN15" s="101"/>
+      <c r="AO15" s="101"/>
+      <c r="AP15" s="101"/>
+      <c r="AQ15" s="101"/>
+      <c r="AR15" s="101"/>
+      <c r="AS15" s="100"/>
+      <c r="AT15" s="101"/>
+      <c r="AU15" s="101"/>
+      <c r="AV15" s="101"/>
+      <c r="AW15" s="101"/>
+      <c r="AX15" s="101"/>
+      <c r="AY15" s="101"/>
+      <c r="AZ15" s="101"/>
+      <c r="BA15" s="100"/>
+      <c r="BB15" s="101"/>
+      <c r="BC15" s="101"/>
+      <c r="BD15" s="101"/>
+      <c r="BE15" s="101"/>
+      <c r="BF15" s="101"/>
+      <c r="BG15" s="101"/>
+      <c r="BH15" s="101"/>
+      <c r="BI15" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ15" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK15" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL15" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM15" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN15" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO15" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP15" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR15" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="16" spans="2:71" x14ac:dyDescent="0.2">
+      <c r="B16" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E16" s="100"/>
+      <c r="F16" s="101"/>
+      <c r="G16" s="101"/>
+      <c r="H16" s="101"/>
+      <c r="I16" s="101"/>
+      <c r="J16" s="101"/>
+      <c r="K16" s="101"/>
+      <c r="L16" s="101"/>
+      <c r="M16" s="100"/>
+      <c r="N16" s="101"/>
+      <c r="O16" s="101"/>
+      <c r="P16" s="101"/>
+      <c r="Q16" s="101"/>
+      <c r="R16" s="101"/>
+      <c r="S16" s="101"/>
+      <c r="T16" s="101"/>
+      <c r="U16" s="100"/>
+      <c r="V16" s="101"/>
+      <c r="W16" s="101"/>
+      <c r="X16" s="101"/>
+      <c r="Y16" s="101"/>
+      <c r="Z16" s="101"/>
+      <c r="AA16" s="101"/>
+      <c r="AB16" s="101"/>
+      <c r="AC16" s="100"/>
+      <c r="AD16" s="101"/>
+      <c r="AE16" s="101"/>
+      <c r="AF16" s="101"/>
+      <c r="AG16" s="101"/>
+      <c r="AH16" s="101"/>
+      <c r="AI16" s="101"/>
+      <c r="AJ16" s="101"/>
+      <c r="AK16" s="100"/>
+      <c r="AL16" s="101"/>
+      <c r="AM16" s="101"/>
+      <c r="AN16" s="101"/>
+      <c r="AO16" s="101"/>
+      <c r="AP16" s="101"/>
+      <c r="AQ16" s="101"/>
+      <c r="AR16" s="101"/>
+      <c r="AS16" s="100"/>
+      <c r="AT16" s="101"/>
+      <c r="AU16" s="101"/>
+      <c r="AV16" s="101"/>
+      <c r="AW16" s="101"/>
+      <c r="AX16" s="101"/>
+      <c r="AY16" s="101"/>
+      <c r="AZ16" s="101"/>
+      <c r="BA16" s="100"/>
+      <c r="BB16" s="101"/>
+      <c r="BC16" s="101"/>
+      <c r="BD16" s="101"/>
+      <c r="BE16" s="101"/>
+      <c r="BF16" s="101"/>
+      <c r="BG16" s="101"/>
+      <c r="BH16" s="101"/>
+      <c r="BI16" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ16" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK16" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL16" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM16" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN16" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO16" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP16" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR16" s="7" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B17" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E17" s="100"/>
+      <c r="F17" s="101"/>
+      <c r="G17" s="101"/>
+      <c r="H17" s="101"/>
+      <c r="I17" s="101"/>
+      <c r="J17" s="101"/>
+      <c r="K17" s="101"/>
+      <c r="L17" s="101"/>
+      <c r="M17" s="100"/>
+      <c r="N17" s="101"/>
+      <c r="O17" s="101"/>
+      <c r="P17" s="101"/>
+      <c r="Q17" s="101"/>
+      <c r="R17" s="101"/>
+      <c r="S17" s="101"/>
+      <c r="T17" s="101"/>
+      <c r="U17" s="100"/>
+      <c r="V17" s="101"/>
+      <c r="W17" s="101"/>
+      <c r="X17" s="101"/>
+      <c r="Y17" s="101"/>
+      <c r="Z17" s="101"/>
+      <c r="AA17" s="101"/>
+      <c r="AB17" s="101"/>
+      <c r="AC17" s="100"/>
+      <c r="AD17" s="101"/>
+      <c r="AE17" s="101"/>
+      <c r="AF17" s="101"/>
+      <c r="AG17" s="101"/>
+      <c r="AH17" s="101"/>
+      <c r="AI17" s="101"/>
+      <c r="AJ17" s="101"/>
+      <c r="AK17" s="100"/>
+      <c r="AL17" s="101"/>
+      <c r="AM17" s="101"/>
+      <c r="AN17" s="101"/>
+      <c r="AO17" s="101"/>
+      <c r="AP17" s="101"/>
+      <c r="AQ17" s="101"/>
+      <c r="AR17" s="101"/>
+      <c r="AS17" s="100"/>
+      <c r="AT17" s="101"/>
+      <c r="AU17" s="101"/>
+      <c r="AV17" s="101"/>
+      <c r="AW17" s="101"/>
+      <c r="AX17" s="101"/>
+      <c r="AY17" s="101"/>
+      <c r="AZ17" s="101"/>
+      <c r="BA17" s="100"/>
+      <c r="BB17" s="101"/>
+      <c r="BC17" s="101"/>
+      <c r="BD17" s="101"/>
+      <c r="BE17" s="101"/>
+      <c r="BF17" s="101"/>
+      <c r="BG17" s="101"/>
+      <c r="BH17" s="101"/>
+      <c r="BI17" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ17" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK17" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL17" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM17" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN17" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO17" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP17" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR17" s="7" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B18" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E18" s="89" t="s">
+        <v>251</v>
+      </c>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="90"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="90"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="90"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="90"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="90"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="90"/>
+      <c r="AE18" s="90"/>
+      <c r="AF18" s="90"/>
+      <c r="AG18" s="90"/>
+      <c r="AH18" s="90"/>
+      <c r="AI18" s="90"/>
+      <c r="AJ18" s="90"/>
+      <c r="AK18" s="90"/>
+      <c r="AL18" s="90"/>
+      <c r="AM18" s="90"/>
+      <c r="AN18" s="90"/>
+      <c r="AO18" s="90"/>
+      <c r="AP18" s="90"/>
+      <c r="AQ18" s="90"/>
+      <c r="AR18" s="90"/>
+      <c r="AS18" s="90"/>
+      <c r="AT18" s="90"/>
+      <c r="AU18" s="90"/>
+      <c r="AV18" s="90"/>
+      <c r="AW18" s="90"/>
+      <c r="AX18" s="90"/>
+      <c r="AY18" s="90"/>
+      <c r="AZ18" s="90"/>
+      <c r="BA18" s="90"/>
+      <c r="BB18" s="90"/>
+      <c r="BC18" s="90"/>
+      <c r="BD18" s="90"/>
+      <c r="BE18" s="90"/>
+      <c r="BF18" s="90"/>
+      <c r="BG18" s="90"/>
+      <c r="BH18" s="90"/>
+      <c r="BI18" s="90"/>
+      <c r="BJ18" s="90"/>
+      <c r="BK18" s="90"/>
+      <c r="BL18" s="91"/>
+      <c r="BM18" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN18" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO18" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP18" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR18" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B19" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="BM19" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN19" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO19" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP19" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR19" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B20" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="BI20" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ20" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK20" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL20" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM20" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN20" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO20" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP20" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR20" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B21" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="BI21" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ21" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK21" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL21" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM21" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN21" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO21" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP21" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR21" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="22" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B22" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="BI22" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ22" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK22" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL22" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM22" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN22" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO22" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP22" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR22" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B23" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="BI23" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ23" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK23" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL23" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM23" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN23" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO23" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP23" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR23" s="7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="24" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B24" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="BI24" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ24" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK24" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL24" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM24" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN24" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO24" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP24" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR24" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="25" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B25" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="BI25" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ25" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK25" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL25" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM25" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN25" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO25" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP25" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR25" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B26" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="BI26" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ26" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK26" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL26" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM26" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN26" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO26" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP26" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR26" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="27" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B27" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="BI27" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ27" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK27" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL27" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM27" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN27" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO27" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP27" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR27" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B28" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="BI28" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ28" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK28" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL28" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM28" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN28" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO28" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP28" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR28" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="29" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B29" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="BI29" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ29" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK29" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL29" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM29" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN29" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO29" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP29" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR29" s="7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B30" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="BI30" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ30" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK30" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL30" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM30" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN30" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO30" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP30" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR30" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B31" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="BI31" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ31" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK31" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL31" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM31" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN31" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO31" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP31" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR31" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B32" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="BI32" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ32" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK32" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL32" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM32" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN32" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO32" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP32" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR32" s="7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="33" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B33" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="BI33" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ33" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK33" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL33" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM33" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN33" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO33" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP33" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR33" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="34" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B34" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="BI34" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ34" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK34" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL34" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM34" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN34" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO34" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP34" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR34" s="7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="35" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B35" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="BI35" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ35" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK35" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL35" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM35" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN35" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO35" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP35" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR35" s="7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B36" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="BI36" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ36" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK36" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL36" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM36" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN36" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO36" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP36" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR36" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="37" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B37" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="BI37" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ37" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK37" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL37" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM37" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN37" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO37" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP37" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR37" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="38" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B38" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="BI38" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ38" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK38" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL38" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM38" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN38" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO38" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP38" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR38" s="7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="39" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B39" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="BI39" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ39" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK39" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL39" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM39" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN39" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO39" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP39" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR39" s="7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="40" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B40" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="E40" s="102" t="s">
+        <v>250</v>
+      </c>
+      <c r="F40" s="103"/>
+      <c r="G40" s="103"/>
+      <c r="H40" s="103"/>
+      <c r="I40" s="103"/>
+      <c r="J40" s="103"/>
+      <c r="K40" s="103"/>
+      <c r="L40" s="103"/>
+      <c r="M40" s="103"/>
+      <c r="N40" s="103"/>
+      <c r="O40" s="103"/>
+      <c r="P40" s="103"/>
+      <c r="Q40" s="103"/>
+      <c r="R40" s="103"/>
+      <c r="S40" s="103"/>
+      <c r="T40" s="103"/>
+      <c r="U40" s="103"/>
+      <c r="V40" s="103"/>
+      <c r="W40" s="103"/>
+      <c r="X40" s="103"/>
+      <c r="Y40" s="103"/>
+      <c r="Z40" s="103"/>
+      <c r="AA40" s="103"/>
+      <c r="AB40" s="103"/>
+      <c r="AC40" s="103"/>
+      <c r="AD40" s="103"/>
+      <c r="AE40" s="103"/>
+      <c r="AF40" s="103"/>
+      <c r="AG40" s="103"/>
+      <c r="AH40" s="103"/>
+      <c r="AI40" s="103"/>
+      <c r="AJ40" s="103"/>
+      <c r="AK40" s="103"/>
+      <c r="AL40" s="103"/>
+      <c r="AM40" s="103"/>
+      <c r="AN40" s="103"/>
+      <c r="AO40" s="103"/>
+      <c r="AP40" s="103"/>
+      <c r="AQ40" s="103"/>
+      <c r="AR40" s="103"/>
+      <c r="AS40" s="103"/>
+      <c r="AT40" s="103"/>
+      <c r="AU40" s="103"/>
+      <c r="AV40" s="103"/>
+      <c r="AW40" s="103"/>
+      <c r="AX40" s="103"/>
+      <c r="AY40" s="103"/>
+      <c r="AZ40" s="103"/>
+      <c r="BA40" s="103"/>
+      <c r="BB40" s="103"/>
+      <c r="BC40" s="103"/>
+      <c r="BD40" s="103"/>
+      <c r="BE40" s="103"/>
+      <c r="BF40" s="103"/>
+      <c r="BG40" s="103"/>
+      <c r="BH40" s="104"/>
+      <c r="BI40" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ40" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK40" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL40" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM40" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN40" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO40" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP40" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR40" s="7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="41" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B41" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E41" s="105"/>
+      <c r="F41" s="106"/>
+      <c r="G41" s="106"/>
+      <c r="H41" s="106"/>
+      <c r="I41" s="106"/>
+      <c r="J41" s="106"/>
+      <c r="K41" s="106"/>
+      <c r="L41" s="106"/>
+      <c r="M41" s="106"/>
+      <c r="N41" s="106"/>
+      <c r="O41" s="106"/>
+      <c r="P41" s="106"/>
+      <c r="Q41" s="106"/>
+      <c r="R41" s="106"/>
+      <c r="S41" s="106"/>
+      <c r="T41" s="106"/>
+      <c r="U41" s="106"/>
+      <c r="V41" s="106"/>
+      <c r="W41" s="106"/>
+      <c r="X41" s="106"/>
+      <c r="Y41" s="106"/>
+      <c r="Z41" s="106"/>
+      <c r="AA41" s="106"/>
+      <c r="AB41" s="106"/>
+      <c r="AC41" s="106"/>
+      <c r="AD41" s="106"/>
+      <c r="AE41" s="106"/>
+      <c r="AF41" s="106"/>
+      <c r="AG41" s="106"/>
+      <c r="AH41" s="106"/>
+      <c r="AI41" s="106"/>
+      <c r="AJ41" s="106"/>
+      <c r="AK41" s="106"/>
+      <c r="AL41" s="106"/>
+      <c r="AM41" s="106"/>
+      <c r="AN41" s="106"/>
+      <c r="AO41" s="106"/>
+      <c r="AP41" s="106"/>
+      <c r="AQ41" s="106"/>
+      <c r="AR41" s="106"/>
+      <c r="AS41" s="106"/>
+      <c r="AT41" s="106"/>
+      <c r="AU41" s="106"/>
+      <c r="AV41" s="106"/>
+      <c r="AW41" s="106"/>
+      <c r="AX41" s="106"/>
+      <c r="AY41" s="106"/>
+      <c r="AZ41" s="106"/>
+      <c r="BA41" s="106"/>
+      <c r="BB41" s="106"/>
+      <c r="BC41" s="106"/>
+      <c r="BD41" s="106"/>
+      <c r="BE41" s="106"/>
+      <c r="BF41" s="106"/>
+      <c r="BG41" s="106"/>
+      <c r="BH41" s="107"/>
+      <c r="BI41" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ41" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK41" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL41" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM41" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN41" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO41" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP41" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR41" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="42" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B42" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="E42" s="105"/>
+      <c r="F42" s="106"/>
+      <c r="G42" s="106"/>
+      <c r="H42" s="106"/>
+      <c r="I42" s="106"/>
+      <c r="J42" s="106"/>
+      <c r="K42" s="106"/>
+      <c r="L42" s="106"/>
+      <c r="M42" s="106"/>
+      <c r="N42" s="106"/>
+      <c r="O42" s="106"/>
+      <c r="P42" s="106"/>
+      <c r="Q42" s="106"/>
+      <c r="R42" s="106"/>
+      <c r="S42" s="106"/>
+      <c r="T42" s="106"/>
+      <c r="U42" s="106"/>
+      <c r="V42" s="106"/>
+      <c r="W42" s="106"/>
+      <c r="X42" s="106"/>
+      <c r="Y42" s="106"/>
+      <c r="Z42" s="106"/>
+      <c r="AA42" s="106"/>
+      <c r="AB42" s="106"/>
+      <c r="AC42" s="106"/>
+      <c r="AD42" s="106"/>
+      <c r="AE42" s="106"/>
+      <c r="AF42" s="106"/>
+      <c r="AG42" s="106"/>
+      <c r="AH42" s="106"/>
+      <c r="AI42" s="106"/>
+      <c r="AJ42" s="106"/>
+      <c r="AK42" s="106"/>
+      <c r="AL42" s="106"/>
+      <c r="AM42" s="106"/>
+      <c r="AN42" s="106"/>
+      <c r="AO42" s="106"/>
+      <c r="AP42" s="106"/>
+      <c r="AQ42" s="106"/>
+      <c r="AR42" s="106"/>
+      <c r="AS42" s="106"/>
+      <c r="AT42" s="106"/>
+      <c r="AU42" s="106"/>
+      <c r="AV42" s="106"/>
+      <c r="AW42" s="106"/>
+      <c r="AX42" s="106"/>
+      <c r="AY42" s="106"/>
+      <c r="AZ42" s="106"/>
+      <c r="BA42" s="106"/>
+      <c r="BB42" s="106"/>
+      <c r="BC42" s="106"/>
+      <c r="BD42" s="106"/>
+      <c r="BE42" s="106"/>
+      <c r="BF42" s="106"/>
+      <c r="BG42" s="106"/>
+      <c r="BH42" s="107"/>
+      <c r="BI42" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ42" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK42" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL42" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM42" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN42" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO42" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP42" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR42" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="43" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B43" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="E43" s="105"/>
+      <c r="F43" s="106"/>
+      <c r="G43" s="106"/>
+      <c r="H43" s="106"/>
+      <c r="I43" s="106"/>
+      <c r="J43" s="106"/>
+      <c r="K43" s="106"/>
+      <c r="L43" s="106"/>
+      <c r="M43" s="106"/>
+      <c r="N43" s="106"/>
+      <c r="O43" s="106"/>
+      <c r="P43" s="106"/>
+      <c r="Q43" s="106"/>
+      <c r="R43" s="106"/>
+      <c r="S43" s="106"/>
+      <c r="T43" s="106"/>
+      <c r="U43" s="106"/>
+      <c r="V43" s="106"/>
+      <c r="W43" s="106"/>
+      <c r="X43" s="106"/>
+      <c r="Y43" s="106"/>
+      <c r="Z43" s="106"/>
+      <c r="AA43" s="106"/>
+      <c r="AB43" s="106"/>
+      <c r="AC43" s="106"/>
+      <c r="AD43" s="106"/>
+      <c r="AE43" s="106"/>
+      <c r="AF43" s="106"/>
+      <c r="AG43" s="106"/>
+      <c r="AH43" s="106"/>
+      <c r="AI43" s="106"/>
+      <c r="AJ43" s="106"/>
+      <c r="AK43" s="106"/>
+      <c r="AL43" s="106"/>
+      <c r="AM43" s="106"/>
+      <c r="AN43" s="106"/>
+      <c r="AO43" s="106"/>
+      <c r="AP43" s="106"/>
+      <c r="AQ43" s="106"/>
+      <c r="AR43" s="106"/>
+      <c r="AS43" s="106"/>
+      <c r="AT43" s="106"/>
+      <c r="AU43" s="106"/>
+      <c r="AV43" s="106"/>
+      <c r="AW43" s="106"/>
+      <c r="AX43" s="106"/>
+      <c r="AY43" s="106"/>
+      <c r="AZ43" s="106"/>
+      <c r="BA43" s="106"/>
+      <c r="BB43" s="106"/>
+      <c r="BC43" s="106"/>
+      <c r="BD43" s="106"/>
+      <c r="BE43" s="106"/>
+      <c r="BF43" s="106"/>
+      <c r="BG43" s="106"/>
+      <c r="BH43" s="107"/>
+      <c r="BI43" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ43" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK43" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL43" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM43" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN43" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO43" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP43" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR43" s="7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="44" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B44" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="E44" s="105"/>
+      <c r="F44" s="106"/>
+      <c r="G44" s="106"/>
+      <c r="H44" s="106"/>
+      <c r="I44" s="106"/>
+      <c r="J44" s="106"/>
+      <c r="K44" s="106"/>
+      <c r="L44" s="106"/>
+      <c r="M44" s="106"/>
+      <c r="N44" s="106"/>
+      <c r="O44" s="106"/>
+      <c r="P44" s="106"/>
+      <c r="Q44" s="106"/>
+      <c r="R44" s="106"/>
+      <c r="S44" s="106"/>
+      <c r="T44" s="106"/>
+      <c r="U44" s="106"/>
+      <c r="V44" s="106"/>
+      <c r="W44" s="106"/>
+      <c r="X44" s="106"/>
+      <c r="Y44" s="106"/>
+      <c r="Z44" s="106"/>
+      <c r="AA44" s="106"/>
+      <c r="AB44" s="106"/>
+      <c r="AC44" s="106"/>
+      <c r="AD44" s="106"/>
+      <c r="AE44" s="106"/>
+      <c r="AF44" s="106"/>
+      <c r="AG44" s="106"/>
+      <c r="AH44" s="106"/>
+      <c r="AI44" s="106"/>
+      <c r="AJ44" s="106"/>
+      <c r="AK44" s="106"/>
+      <c r="AL44" s="106"/>
+      <c r="AM44" s="106"/>
+      <c r="AN44" s="106"/>
+      <c r="AO44" s="106"/>
+      <c r="AP44" s="106"/>
+      <c r="AQ44" s="106"/>
+      <c r="AR44" s="106"/>
+      <c r="AS44" s="106"/>
+      <c r="AT44" s="106"/>
+      <c r="AU44" s="106"/>
+      <c r="AV44" s="106"/>
+      <c r="AW44" s="106"/>
+      <c r="AX44" s="106"/>
+      <c r="AY44" s="106"/>
+      <c r="AZ44" s="106"/>
+      <c r="BA44" s="106"/>
+      <c r="BB44" s="106"/>
+      <c r="BC44" s="106"/>
+      <c r="BD44" s="106"/>
+      <c r="BE44" s="106"/>
+      <c r="BF44" s="106"/>
+      <c r="BG44" s="106"/>
+      <c r="BH44" s="107"/>
+      <c r="BI44" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ44" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK44" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL44" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM44" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN44" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO44" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP44" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR44" s="7" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="45" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B45" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="E45" s="105"/>
+      <c r="F45" s="106"/>
+      <c r="G45" s="106"/>
+      <c r="H45" s="106"/>
+      <c r="I45" s="106"/>
+      <c r="J45" s="106"/>
+      <c r="K45" s="106"/>
+      <c r="L45" s="106"/>
+      <c r="M45" s="106"/>
+      <c r="N45" s="106"/>
+      <c r="O45" s="106"/>
+      <c r="P45" s="106"/>
+      <c r="Q45" s="106"/>
+      <c r="R45" s="106"/>
+      <c r="S45" s="106"/>
+      <c r="T45" s="106"/>
+      <c r="U45" s="106"/>
+      <c r="V45" s="106"/>
+      <c r="W45" s="106"/>
+      <c r="X45" s="106"/>
+      <c r="Y45" s="106"/>
+      <c r="Z45" s="106"/>
+      <c r="AA45" s="106"/>
+      <c r="AB45" s="106"/>
+      <c r="AC45" s="106"/>
+      <c r="AD45" s="106"/>
+      <c r="AE45" s="106"/>
+      <c r="AF45" s="106"/>
+      <c r="AG45" s="106"/>
+      <c r="AH45" s="106"/>
+      <c r="AI45" s="106"/>
+      <c r="AJ45" s="106"/>
+      <c r="AK45" s="106"/>
+      <c r="AL45" s="106"/>
+      <c r="AM45" s="106"/>
+      <c r="AN45" s="106"/>
+      <c r="AO45" s="106"/>
+      <c r="AP45" s="106"/>
+      <c r="AQ45" s="106"/>
+      <c r="AR45" s="106"/>
+      <c r="AS45" s="106"/>
+      <c r="AT45" s="106"/>
+      <c r="AU45" s="106"/>
+      <c r="AV45" s="106"/>
+      <c r="AW45" s="106"/>
+      <c r="AX45" s="106"/>
+      <c r="AY45" s="106"/>
+      <c r="AZ45" s="106"/>
+      <c r="BA45" s="106"/>
+      <c r="BB45" s="106"/>
+      <c r="BC45" s="106"/>
+      <c r="BD45" s="106"/>
+      <c r="BE45" s="106"/>
+      <c r="BF45" s="106"/>
+      <c r="BG45" s="106"/>
+      <c r="BH45" s="107"/>
+      <c r="BI45" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ45" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK45" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL45" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM45" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN45" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO45" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP45" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR45" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="46" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B46" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E46" s="108"/>
+      <c r="F46" s="109"/>
+      <c r="G46" s="109"/>
+      <c r="H46" s="109"/>
+      <c r="I46" s="109"/>
+      <c r="J46" s="109"/>
+      <c r="K46" s="109"/>
+      <c r="L46" s="109"/>
+      <c r="M46" s="109"/>
+      <c r="N46" s="109"/>
+      <c r="O46" s="109"/>
+      <c r="P46" s="109"/>
+      <c r="Q46" s="109"/>
+      <c r="R46" s="109"/>
+      <c r="S46" s="109"/>
+      <c r="T46" s="109"/>
+      <c r="U46" s="109"/>
+      <c r="V46" s="109"/>
+      <c r="W46" s="109"/>
+      <c r="X46" s="109"/>
+      <c r="Y46" s="109"/>
+      <c r="Z46" s="109"/>
+      <c r="AA46" s="109"/>
+      <c r="AB46" s="109"/>
+      <c r="AC46" s="109"/>
+      <c r="AD46" s="109"/>
+      <c r="AE46" s="109"/>
+      <c r="AF46" s="109"/>
+      <c r="AG46" s="109"/>
+      <c r="AH46" s="109"/>
+      <c r="AI46" s="109"/>
+      <c r="AJ46" s="109"/>
+      <c r="AK46" s="109"/>
+      <c r="AL46" s="109"/>
+      <c r="AM46" s="109"/>
+      <c r="AN46" s="109"/>
+      <c r="AO46" s="109"/>
+      <c r="AP46" s="109"/>
+      <c r="AQ46" s="109"/>
+      <c r="AR46" s="109"/>
+      <c r="AS46" s="109"/>
+      <c r="AT46" s="109"/>
+      <c r="AU46" s="109"/>
+      <c r="AV46" s="109"/>
+      <c r="AW46" s="109"/>
+      <c r="AX46" s="109"/>
+      <c r="AY46" s="109"/>
+      <c r="AZ46" s="109"/>
+      <c r="BA46" s="109"/>
+      <c r="BB46" s="109"/>
+      <c r="BC46" s="109"/>
+      <c r="BD46" s="109"/>
+      <c r="BE46" s="109"/>
+      <c r="BF46" s="109"/>
+      <c r="BG46" s="109"/>
+      <c r="BH46" s="110"/>
+      <c r="BI46" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ46" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK46" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL46" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM46" s="10">
+        <v>0</v>
+      </c>
+      <c r="BN46" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO46" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP46" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR46" s="7" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="47" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B47" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E47" s="89" t="s">
+        <v>247</v>
+      </c>
+      <c r="F47" s="90"/>
+      <c r="G47" s="90"/>
+      <c r="H47" s="90"/>
+      <c r="I47" s="90"/>
+      <c r="J47" s="90"/>
+      <c r="K47" s="90"/>
+      <c r="L47" s="90"/>
+      <c r="M47" s="90"/>
+      <c r="N47" s="90"/>
+      <c r="O47" s="90"/>
+      <c r="P47" s="90"/>
+      <c r="Q47" s="90"/>
+      <c r="R47" s="90"/>
+      <c r="S47" s="90"/>
+      <c r="T47" s="90"/>
+      <c r="U47" s="90"/>
+      <c r="V47" s="90"/>
+      <c r="W47" s="90"/>
+      <c r="X47" s="90"/>
+      <c r="Y47" s="90"/>
+      <c r="Z47" s="90"/>
+      <c r="AA47" s="90"/>
+      <c r="AB47" s="90"/>
+      <c r="AC47" s="90"/>
+      <c r="AD47" s="90"/>
+      <c r="AE47" s="90"/>
+      <c r="AF47" s="90"/>
+      <c r="AG47" s="90"/>
+      <c r="AH47" s="90"/>
+      <c r="AI47" s="90"/>
+      <c r="AJ47" s="90"/>
+      <c r="AK47" s="90"/>
+      <c r="AL47" s="90"/>
+      <c r="AM47" s="90"/>
+      <c r="AN47" s="90"/>
+      <c r="AO47" s="90"/>
+      <c r="AP47" s="90"/>
+      <c r="AQ47" s="90"/>
+      <c r="AR47" s="90"/>
+      <c r="AS47" s="90"/>
+      <c r="AT47" s="90"/>
+      <c r="AU47" s="90"/>
+      <c r="AV47" s="90"/>
+      <c r="AW47" s="90"/>
+      <c r="AX47" s="90"/>
+      <c r="AY47" s="90"/>
+      <c r="AZ47" s="90"/>
+      <c r="BA47" s="90"/>
+      <c r="BB47" s="90"/>
+      <c r="BC47" s="90"/>
+      <c r="BD47" s="90"/>
+      <c r="BE47" s="90"/>
+      <c r="BF47" s="90"/>
+      <c r="BG47" s="90"/>
+      <c r="BH47" s="90"/>
+      <c r="BI47" s="90"/>
+      <c r="BJ47" s="90"/>
+      <c r="BK47" s="90"/>
+      <c r="BL47" s="91"/>
+      <c r="BM47" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN47" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO47" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP47" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR47" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="48" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B48" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="E48" s="102" t="s">
+        <v>250</v>
+      </c>
+      <c r="F48" s="103"/>
+      <c r="G48" s="103"/>
+      <c r="H48" s="103"/>
+      <c r="I48" s="103"/>
+      <c r="J48" s="103"/>
+      <c r="K48" s="103"/>
+      <c r="L48" s="103"/>
+      <c r="M48" s="103"/>
+      <c r="N48" s="103"/>
+      <c r="O48" s="103"/>
+      <c r="P48" s="103"/>
+      <c r="Q48" s="103"/>
+      <c r="R48" s="103"/>
+      <c r="S48" s="103"/>
+      <c r="T48" s="103"/>
+      <c r="U48" s="103"/>
+      <c r="V48" s="103"/>
+      <c r="W48" s="103"/>
+      <c r="X48" s="103"/>
+      <c r="Y48" s="103"/>
+      <c r="Z48" s="103"/>
+      <c r="AA48" s="103"/>
+      <c r="AB48" s="103"/>
+      <c r="AC48" s="103"/>
+      <c r="AD48" s="103"/>
+      <c r="AE48" s="103"/>
+      <c r="AF48" s="103"/>
+      <c r="AG48" s="103"/>
+      <c r="AH48" s="103"/>
+      <c r="AI48" s="103"/>
+      <c r="AJ48" s="103"/>
+      <c r="AK48" s="103"/>
+      <c r="AL48" s="103"/>
+      <c r="AM48" s="103"/>
+      <c r="AN48" s="103"/>
+      <c r="AO48" s="103"/>
+      <c r="AP48" s="103"/>
+      <c r="AQ48" s="103"/>
+      <c r="AR48" s="103"/>
+      <c r="AS48" s="103"/>
+      <c r="AT48" s="103"/>
+      <c r="AU48" s="103"/>
+      <c r="AV48" s="103"/>
+      <c r="AW48" s="103"/>
+      <c r="AX48" s="103"/>
+      <c r="AY48" s="103"/>
+      <c r="AZ48" s="103"/>
+      <c r="BA48" s="103"/>
+      <c r="BB48" s="103"/>
+      <c r="BC48" s="103"/>
+      <c r="BD48" s="103"/>
+      <c r="BE48" s="103"/>
+      <c r="BF48" s="103"/>
+      <c r="BG48" s="103"/>
+      <c r="BH48" s="104"/>
+      <c r="BI48" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ48" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK48" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL48" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM48" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN48" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO48" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP48" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR48" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="49" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B49" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E49" s="105"/>
+      <c r="F49" s="106"/>
+      <c r="G49" s="106"/>
+      <c r="H49" s="106"/>
+      <c r="I49" s="106"/>
+      <c r="J49" s="106"/>
+      <c r="K49" s="106"/>
+      <c r="L49" s="106"/>
+      <c r="M49" s="106"/>
+      <c r="N49" s="106"/>
+      <c r="O49" s="106"/>
+      <c r="P49" s="106"/>
+      <c r="Q49" s="106"/>
+      <c r="R49" s="106"/>
+      <c r="S49" s="106"/>
+      <c r="T49" s="106"/>
+      <c r="U49" s="106"/>
+      <c r="V49" s="106"/>
+      <c r="W49" s="106"/>
+      <c r="X49" s="106"/>
+      <c r="Y49" s="106"/>
+      <c r="Z49" s="106"/>
+      <c r="AA49" s="106"/>
+      <c r="AB49" s="106"/>
+      <c r="AC49" s="106"/>
+      <c r="AD49" s="106"/>
+      <c r="AE49" s="106"/>
+      <c r="AF49" s="106"/>
+      <c r="AG49" s="106"/>
+      <c r="AH49" s="106"/>
+      <c r="AI49" s="106"/>
+      <c r="AJ49" s="106"/>
+      <c r="AK49" s="106"/>
+      <c r="AL49" s="106"/>
+      <c r="AM49" s="106"/>
+      <c r="AN49" s="106"/>
+      <c r="AO49" s="106"/>
+      <c r="AP49" s="106"/>
+      <c r="AQ49" s="106"/>
+      <c r="AR49" s="106"/>
+      <c r="AS49" s="106"/>
+      <c r="AT49" s="106"/>
+      <c r="AU49" s="106"/>
+      <c r="AV49" s="106"/>
+      <c r="AW49" s="106"/>
+      <c r="AX49" s="106"/>
+      <c r="AY49" s="106"/>
+      <c r="AZ49" s="106"/>
+      <c r="BA49" s="106"/>
+      <c r="BB49" s="106"/>
+      <c r="BC49" s="106"/>
+      <c r="BD49" s="106"/>
+      <c r="BE49" s="106"/>
+      <c r="BF49" s="106"/>
+      <c r="BG49" s="106"/>
+      <c r="BH49" s="107"/>
+      <c r="BI49" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ49" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK49" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL49" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM49" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN49" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO49" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP49" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR49" s="7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="50" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B50" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E50" s="105"/>
+      <c r="F50" s="106"/>
+      <c r="G50" s="106"/>
+      <c r="H50" s="106"/>
+      <c r="I50" s="106"/>
+      <c r="J50" s="106"/>
+      <c r="K50" s="106"/>
+      <c r="L50" s="106"/>
+      <c r="M50" s="106"/>
+      <c r="N50" s="106"/>
+      <c r="O50" s="106"/>
+      <c r="P50" s="106"/>
+      <c r="Q50" s="106"/>
+      <c r="R50" s="106"/>
+      <c r="S50" s="106"/>
+      <c r="T50" s="106"/>
+      <c r="U50" s="106"/>
+      <c r="V50" s="106"/>
+      <c r="W50" s="106"/>
+      <c r="X50" s="106"/>
+      <c r="Y50" s="106"/>
+      <c r="Z50" s="106"/>
+      <c r="AA50" s="106"/>
+      <c r="AB50" s="106"/>
+      <c r="AC50" s="106"/>
+      <c r="AD50" s="106"/>
+      <c r="AE50" s="106"/>
+      <c r="AF50" s="106"/>
+      <c r="AG50" s="106"/>
+      <c r="AH50" s="106"/>
+      <c r="AI50" s="106"/>
+      <c r="AJ50" s="106"/>
+      <c r="AK50" s="106"/>
+      <c r="AL50" s="106"/>
+      <c r="AM50" s="106"/>
+      <c r="AN50" s="106"/>
+      <c r="AO50" s="106"/>
+      <c r="AP50" s="106"/>
+      <c r="AQ50" s="106"/>
+      <c r="AR50" s="106"/>
+      <c r="AS50" s="106"/>
+      <c r="AT50" s="106"/>
+      <c r="AU50" s="106"/>
+      <c r="AV50" s="106"/>
+      <c r="AW50" s="106"/>
+      <c r="AX50" s="106"/>
+      <c r="AY50" s="106"/>
+      <c r="AZ50" s="106"/>
+      <c r="BA50" s="106"/>
+      <c r="BB50" s="106"/>
+      <c r="BC50" s="106"/>
+      <c r="BD50" s="106"/>
+      <c r="BE50" s="106"/>
+      <c r="BF50" s="106"/>
+      <c r="BG50" s="106"/>
+      <c r="BH50" s="107"/>
+      <c r="BI50" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ50" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK50" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL50" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM50" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN50" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO50" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP50" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR50" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="51" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B51" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="E51" s="105"/>
+      <c r="F51" s="106"/>
+      <c r="G51" s="106"/>
+      <c r="H51" s="106"/>
+      <c r="I51" s="106"/>
+      <c r="J51" s="106"/>
+      <c r="K51" s="106"/>
+      <c r="L51" s="106"/>
+      <c r="M51" s="106"/>
+      <c r="N51" s="106"/>
+      <c r="O51" s="106"/>
+      <c r="P51" s="106"/>
+      <c r="Q51" s="106"/>
+      <c r="R51" s="106"/>
+      <c r="S51" s="106"/>
+      <c r="T51" s="106"/>
+      <c r="U51" s="106"/>
+      <c r="V51" s="106"/>
+      <c r="W51" s="106"/>
+      <c r="X51" s="106"/>
+      <c r="Y51" s="106"/>
+      <c r="Z51" s="106"/>
+      <c r="AA51" s="106"/>
+      <c r="AB51" s="106"/>
+      <c r="AC51" s="106"/>
+      <c r="AD51" s="106"/>
+      <c r="AE51" s="106"/>
+      <c r="AF51" s="106"/>
+      <c r="AG51" s="106"/>
+      <c r="AH51" s="106"/>
+      <c r="AI51" s="106"/>
+      <c r="AJ51" s="106"/>
+      <c r="AK51" s="106"/>
+      <c r="AL51" s="106"/>
+      <c r="AM51" s="106"/>
+      <c r="AN51" s="106"/>
+      <c r="AO51" s="106"/>
+      <c r="AP51" s="106"/>
+      <c r="AQ51" s="106"/>
+      <c r="AR51" s="106"/>
+      <c r="AS51" s="106"/>
+      <c r="AT51" s="106"/>
+      <c r="AU51" s="106"/>
+      <c r="AV51" s="106"/>
+      <c r="AW51" s="106"/>
+      <c r="AX51" s="106"/>
+      <c r="AY51" s="106"/>
+      <c r="AZ51" s="106"/>
+      <c r="BA51" s="106"/>
+      <c r="BB51" s="106"/>
+      <c r="BC51" s="106"/>
+      <c r="BD51" s="106"/>
+      <c r="BE51" s="106"/>
+      <c r="BF51" s="106"/>
+      <c r="BG51" s="106"/>
+      <c r="BH51" s="107"/>
+      <c r="BI51" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ51" s="10">
+        <v>0</v>
+      </c>
+      <c r="BK51" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL51" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM51" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN51" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO51" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP51" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR51" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="52" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B52" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="E52" s="105"/>
+      <c r="F52" s="106"/>
+      <c r="G52" s="106"/>
+      <c r="H52" s="106"/>
+      <c r="I52" s="106"/>
+      <c r="J52" s="106"/>
+      <c r="K52" s="106"/>
+      <c r="L52" s="106"/>
+      <c r="M52" s="106"/>
+      <c r="N52" s="106"/>
+      <c r="O52" s="106"/>
+      <c r="P52" s="106"/>
+      <c r="Q52" s="106"/>
+      <c r="R52" s="106"/>
+      <c r="S52" s="106"/>
+      <c r="T52" s="106"/>
+      <c r="U52" s="106"/>
+      <c r="V52" s="106"/>
+      <c r="W52" s="106"/>
+      <c r="X52" s="106"/>
+      <c r="Y52" s="106"/>
+      <c r="Z52" s="106"/>
+      <c r="AA52" s="106"/>
+      <c r="AB52" s="106"/>
+      <c r="AC52" s="106"/>
+      <c r="AD52" s="106"/>
+      <c r="AE52" s="106"/>
+      <c r="AF52" s="106"/>
+      <c r="AG52" s="106"/>
+      <c r="AH52" s="106"/>
+      <c r="AI52" s="106"/>
+      <c r="AJ52" s="106"/>
+      <c r="AK52" s="106"/>
+      <c r="AL52" s="106"/>
+      <c r="AM52" s="106"/>
+      <c r="AN52" s="106"/>
+      <c r="AO52" s="106"/>
+      <c r="AP52" s="106"/>
+      <c r="AQ52" s="106"/>
+      <c r="AR52" s="106"/>
+      <c r="AS52" s="106"/>
+      <c r="AT52" s="106"/>
+      <c r="AU52" s="106"/>
+      <c r="AV52" s="106"/>
+      <c r="AW52" s="106"/>
+      <c r="AX52" s="106"/>
+      <c r="AY52" s="106"/>
+      <c r="AZ52" s="106"/>
+      <c r="BA52" s="106"/>
+      <c r="BB52" s="106"/>
+      <c r="BC52" s="106"/>
+      <c r="BD52" s="106"/>
+      <c r="BE52" s="106"/>
+      <c r="BF52" s="106"/>
+      <c r="BG52" s="106"/>
+      <c r="BH52" s="107"/>
+      <c r="BI52" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ52" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK52" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL52" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM52" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN52" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO52" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP52" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR52" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="53" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B53" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="E53" s="105"/>
+      <c r="F53" s="106"/>
+      <c r="G53" s="106"/>
+      <c r="H53" s="106"/>
+      <c r="I53" s="106"/>
+      <c r="J53" s="106"/>
+      <c r="K53" s="106"/>
+      <c r="L53" s="106"/>
+      <c r="M53" s="106"/>
+      <c r="N53" s="106"/>
+      <c r="O53" s="106"/>
+      <c r="P53" s="106"/>
+      <c r="Q53" s="106"/>
+      <c r="R53" s="106"/>
+      <c r="S53" s="106"/>
+      <c r="T53" s="106"/>
+      <c r="U53" s="106"/>
+      <c r="V53" s="106"/>
+      <c r="W53" s="106"/>
+      <c r="X53" s="106"/>
+      <c r="Y53" s="106"/>
+      <c r="Z53" s="106"/>
+      <c r="AA53" s="106"/>
+      <c r="AB53" s="106"/>
+      <c r="AC53" s="106"/>
+      <c r="AD53" s="106"/>
+      <c r="AE53" s="106"/>
+      <c r="AF53" s="106"/>
+      <c r="AG53" s="106"/>
+      <c r="AH53" s="106"/>
+      <c r="AI53" s="106"/>
+      <c r="AJ53" s="106"/>
+      <c r="AK53" s="106"/>
+      <c r="AL53" s="106"/>
+      <c r="AM53" s="106"/>
+      <c r="AN53" s="106"/>
+      <c r="AO53" s="106"/>
+      <c r="AP53" s="106"/>
+      <c r="AQ53" s="106"/>
+      <c r="AR53" s="106"/>
+      <c r="AS53" s="106"/>
+      <c r="AT53" s="106"/>
+      <c r="AU53" s="106"/>
+      <c r="AV53" s="106"/>
+      <c r="AW53" s="106"/>
+      <c r="AX53" s="106"/>
+      <c r="AY53" s="106"/>
+      <c r="AZ53" s="106"/>
+      <c r="BA53" s="106"/>
+      <c r="BB53" s="106"/>
+      <c r="BC53" s="106"/>
+      <c r="BD53" s="106"/>
+      <c r="BE53" s="106"/>
+      <c r="BF53" s="106"/>
+      <c r="BG53" s="106"/>
+      <c r="BH53" s="107"/>
+      <c r="BI53" s="97">
+        <v>0</v>
+      </c>
+      <c r="BJ53" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK53" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL53" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM53" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN53" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO53" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP53" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR53" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="54" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B54" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="E54" s="105"/>
+      <c r="F54" s="106"/>
+      <c r="G54" s="106"/>
+      <c r="H54" s="106"/>
+      <c r="I54" s="106"/>
+      <c r="J54" s="106"/>
+      <c r="K54" s="106"/>
+      <c r="L54" s="106"/>
+      <c r="M54" s="106"/>
+      <c r="N54" s="106"/>
+      <c r="O54" s="106"/>
+      <c r="P54" s="106"/>
+      <c r="Q54" s="106"/>
+      <c r="R54" s="106"/>
+      <c r="S54" s="106"/>
+      <c r="T54" s="106"/>
+      <c r="U54" s="106"/>
+      <c r="V54" s="106"/>
+      <c r="W54" s="106"/>
+      <c r="X54" s="106"/>
+      <c r="Y54" s="106"/>
+      <c r="Z54" s="106"/>
+      <c r="AA54" s="106"/>
+      <c r="AB54" s="106"/>
+      <c r="AC54" s="106"/>
+      <c r="AD54" s="106"/>
+      <c r="AE54" s="106"/>
+      <c r="AF54" s="106"/>
+      <c r="AG54" s="106"/>
+      <c r="AH54" s="106"/>
+      <c r="AI54" s="106"/>
+      <c r="AJ54" s="106"/>
+      <c r="AK54" s="106"/>
+      <c r="AL54" s="106"/>
+      <c r="AM54" s="106"/>
+      <c r="AN54" s="106"/>
+      <c r="AO54" s="106"/>
+      <c r="AP54" s="106"/>
+      <c r="AQ54" s="106"/>
+      <c r="AR54" s="106"/>
+      <c r="AS54" s="106"/>
+      <c r="AT54" s="106"/>
+      <c r="AU54" s="106"/>
+      <c r="AV54" s="106"/>
+      <c r="AW54" s="106"/>
+      <c r="AX54" s="106"/>
+      <c r="AY54" s="106"/>
+      <c r="AZ54" s="106"/>
+      <c r="BA54" s="106"/>
+      <c r="BB54" s="106"/>
+      <c r="BC54" s="106"/>
+      <c r="BD54" s="106"/>
+      <c r="BE54" s="106"/>
+      <c r="BF54" s="106"/>
+      <c r="BG54" s="106"/>
+      <c r="BH54" s="107"/>
+      <c r="BI54" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ54" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK54" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL54" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM54" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN54" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO54" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP54" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR54" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="55" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B55" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="E55" s="105"/>
+      <c r="F55" s="106"/>
+      <c r="G55" s="106"/>
+      <c r="H55" s="106"/>
+      <c r="I55" s="106"/>
+      <c r="J55" s="106"/>
+      <c r="K55" s="106"/>
+      <c r="L55" s="106"/>
+      <c r="M55" s="106"/>
+      <c r="N55" s="106"/>
+      <c r="O55" s="106"/>
+      <c r="P55" s="106"/>
+      <c r="Q55" s="106"/>
+      <c r="R55" s="106"/>
+      <c r="S55" s="106"/>
+      <c r="T55" s="106"/>
+      <c r="U55" s="106"/>
+      <c r="V55" s="106"/>
+      <c r="W55" s="106"/>
+      <c r="X55" s="106"/>
+      <c r="Y55" s="106"/>
+      <c r="Z55" s="106"/>
+      <c r="AA55" s="106"/>
+      <c r="AB55" s="106"/>
+      <c r="AC55" s="106"/>
+      <c r="AD55" s="106"/>
+      <c r="AE55" s="106"/>
+      <c r="AF55" s="106"/>
+      <c r="AG55" s="106"/>
+      <c r="AH55" s="106"/>
+      <c r="AI55" s="106"/>
+      <c r="AJ55" s="106"/>
+      <c r="AK55" s="106"/>
+      <c r="AL55" s="106"/>
+      <c r="AM55" s="106"/>
+      <c r="AN55" s="106"/>
+      <c r="AO55" s="106"/>
+      <c r="AP55" s="106"/>
+      <c r="AQ55" s="106"/>
+      <c r="AR55" s="106"/>
+      <c r="AS55" s="106"/>
+      <c r="AT55" s="106"/>
+      <c r="AU55" s="106"/>
+      <c r="AV55" s="106"/>
+      <c r="AW55" s="106"/>
+      <c r="AX55" s="106"/>
+      <c r="AY55" s="106"/>
+      <c r="AZ55" s="106"/>
+      <c r="BA55" s="106"/>
+      <c r="BB55" s="106"/>
+      <c r="BC55" s="106"/>
+      <c r="BD55" s="106"/>
+      <c r="BE55" s="106"/>
+      <c r="BF55" s="106"/>
+      <c r="BG55" s="106"/>
+      <c r="BH55" s="107"/>
+      <c r="BI55" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ55" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK55" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL55" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM55" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN55" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO55" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP55" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR55" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="56" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B56" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="E56" s="105"/>
+      <c r="F56" s="106"/>
+      <c r="G56" s="106"/>
+      <c r="H56" s="106"/>
+      <c r="I56" s="106"/>
+      <c r="J56" s="106"/>
+      <c r="K56" s="106"/>
+      <c r="L56" s="106"/>
+      <c r="M56" s="106"/>
+      <c r="N56" s="106"/>
+      <c r="O56" s="106"/>
+      <c r="P56" s="106"/>
+      <c r="Q56" s="106"/>
+      <c r="R56" s="106"/>
+      <c r="S56" s="106"/>
+      <c r="T56" s="106"/>
+      <c r="U56" s="106"/>
+      <c r="V56" s="106"/>
+      <c r="W56" s="106"/>
+      <c r="X56" s="106"/>
+      <c r="Y56" s="106"/>
+      <c r="Z56" s="106"/>
+      <c r="AA56" s="106"/>
+      <c r="AB56" s="106"/>
+      <c r="AC56" s="106"/>
+      <c r="AD56" s="106"/>
+      <c r="AE56" s="106"/>
+      <c r="AF56" s="106"/>
+      <c r="AG56" s="106"/>
+      <c r="AH56" s="106"/>
+      <c r="AI56" s="106"/>
+      <c r="AJ56" s="106"/>
+      <c r="AK56" s="106"/>
+      <c r="AL56" s="106"/>
+      <c r="AM56" s="106"/>
+      <c r="AN56" s="106"/>
+      <c r="AO56" s="106"/>
+      <c r="AP56" s="106"/>
+      <c r="AQ56" s="106"/>
+      <c r="AR56" s="106"/>
+      <c r="AS56" s="106"/>
+      <c r="AT56" s="106"/>
+      <c r="AU56" s="106"/>
+      <c r="AV56" s="106"/>
+      <c r="AW56" s="106"/>
+      <c r="AX56" s="106"/>
+      <c r="AY56" s="106"/>
+      <c r="AZ56" s="106"/>
+      <c r="BA56" s="106"/>
+      <c r="BB56" s="106"/>
+      <c r="BC56" s="106"/>
+      <c r="BD56" s="106"/>
+      <c r="BE56" s="106"/>
+      <c r="BF56" s="106"/>
+      <c r="BG56" s="106"/>
+      <c r="BH56" s="107"/>
+      <c r="BI56" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ56" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK56" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL56" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM56" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN56" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO56" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP56" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR56" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="57" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B57" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="E57" s="105"/>
+      <c r="F57" s="106"/>
+      <c r="G57" s="106"/>
+      <c r="H57" s="106"/>
+      <c r="I57" s="106"/>
+      <c r="J57" s="106"/>
+      <c r="K57" s="106"/>
+      <c r="L57" s="106"/>
+      <c r="M57" s="106"/>
+      <c r="N57" s="106"/>
+      <c r="O57" s="106"/>
+      <c r="P57" s="106"/>
+      <c r="Q57" s="106"/>
+      <c r="R57" s="106"/>
+      <c r="S57" s="106"/>
+      <c r="T57" s="106"/>
+      <c r="U57" s="106"/>
+      <c r="V57" s="106"/>
+      <c r="W57" s="106"/>
+      <c r="X57" s="106"/>
+      <c r="Y57" s="106"/>
+      <c r="Z57" s="106"/>
+      <c r="AA57" s="106"/>
+      <c r="AB57" s="106"/>
+      <c r="AC57" s="106"/>
+      <c r="AD57" s="106"/>
+      <c r="AE57" s="106"/>
+      <c r="AF57" s="106"/>
+      <c r="AG57" s="106"/>
+      <c r="AH57" s="106"/>
+      <c r="AI57" s="106"/>
+      <c r="AJ57" s="106"/>
+      <c r="AK57" s="106"/>
+      <c r="AL57" s="106"/>
+      <c r="AM57" s="106"/>
+      <c r="AN57" s="106"/>
+      <c r="AO57" s="106"/>
+      <c r="AP57" s="106"/>
+      <c r="AQ57" s="106"/>
+      <c r="AR57" s="106"/>
+      <c r="AS57" s="106"/>
+      <c r="AT57" s="106"/>
+      <c r="AU57" s="106"/>
+      <c r="AV57" s="106"/>
+      <c r="AW57" s="106"/>
+      <c r="AX57" s="106"/>
+      <c r="AY57" s="106"/>
+      <c r="AZ57" s="106"/>
+      <c r="BA57" s="106"/>
+      <c r="BB57" s="106"/>
+      <c r="BC57" s="106"/>
+      <c r="BD57" s="106"/>
+      <c r="BE57" s="106"/>
+      <c r="BF57" s="106"/>
+      <c r="BG57" s="106"/>
+      <c r="BH57" s="107"/>
+      <c r="BI57" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ57" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK57" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL57" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM57" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN57" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO57" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP57" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR57" s="7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="58" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B58" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="E58" s="105"/>
+      <c r="F58" s="106"/>
+      <c r="G58" s="106"/>
+      <c r="H58" s="106"/>
+      <c r="I58" s="106"/>
+      <c r="J58" s="106"/>
+      <c r="K58" s="106"/>
+      <c r="L58" s="106"/>
+      <c r="M58" s="106"/>
+      <c r="N58" s="106"/>
+      <c r="O58" s="106"/>
+      <c r="P58" s="106"/>
+      <c r="Q58" s="106"/>
+      <c r="R58" s="106"/>
+      <c r="S58" s="106"/>
+      <c r="T58" s="106"/>
+      <c r="U58" s="106"/>
+      <c r="V58" s="106"/>
+      <c r="W58" s="106"/>
+      <c r="X58" s="106"/>
+      <c r="Y58" s="106"/>
+      <c r="Z58" s="106"/>
+      <c r="AA58" s="106"/>
+      <c r="AB58" s="106"/>
+      <c r="AC58" s="106"/>
+      <c r="AD58" s="106"/>
+      <c r="AE58" s="106"/>
+      <c r="AF58" s="106"/>
+      <c r="AG58" s="106"/>
+      <c r="AH58" s="106"/>
+      <c r="AI58" s="106"/>
+      <c r="AJ58" s="106"/>
+      <c r="AK58" s="106"/>
+      <c r="AL58" s="106"/>
+      <c r="AM58" s="106"/>
+      <c r="AN58" s="106"/>
+      <c r="AO58" s="106"/>
+      <c r="AP58" s="106"/>
+      <c r="AQ58" s="106"/>
+      <c r="AR58" s="106"/>
+      <c r="AS58" s="106"/>
+      <c r="AT58" s="106"/>
+      <c r="AU58" s="106"/>
+      <c r="AV58" s="106"/>
+      <c r="AW58" s="106"/>
+      <c r="AX58" s="106"/>
+      <c r="AY58" s="106"/>
+      <c r="AZ58" s="106"/>
+      <c r="BA58" s="106"/>
+      <c r="BB58" s="106"/>
+      <c r="BC58" s="106"/>
+      <c r="BD58" s="106"/>
+      <c r="BE58" s="106"/>
+      <c r="BF58" s="106"/>
+      <c r="BG58" s="106"/>
+      <c r="BH58" s="107"/>
+      <c r="BI58" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ58" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK58" s="10">
+        <v>0</v>
+      </c>
+      <c r="BL58" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM58" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN58" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO58" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP58" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR58" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="59" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B59" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="E59" s="105"/>
+      <c r="F59" s="106"/>
+      <c r="G59" s="106"/>
+      <c r="H59" s="106"/>
+      <c r="I59" s="106"/>
+      <c r="J59" s="106"/>
+      <c r="K59" s="106"/>
+      <c r="L59" s="106"/>
+      <c r="M59" s="106"/>
+      <c r="N59" s="106"/>
+      <c r="O59" s="106"/>
+      <c r="P59" s="106"/>
+      <c r="Q59" s="106"/>
+      <c r="R59" s="106"/>
+      <c r="S59" s="106"/>
+      <c r="T59" s="106"/>
+      <c r="U59" s="106"/>
+      <c r="V59" s="106"/>
+      <c r="W59" s="106"/>
+      <c r="X59" s="106"/>
+      <c r="Y59" s="106"/>
+      <c r="Z59" s="106"/>
+      <c r="AA59" s="106"/>
+      <c r="AB59" s="106"/>
+      <c r="AC59" s="106"/>
+      <c r="AD59" s="106"/>
+      <c r="AE59" s="106"/>
+      <c r="AF59" s="106"/>
+      <c r="AG59" s="106"/>
+      <c r="AH59" s="106"/>
+      <c r="AI59" s="106"/>
+      <c r="AJ59" s="106"/>
+      <c r="AK59" s="106"/>
+      <c r="AL59" s="106"/>
+      <c r="AM59" s="106"/>
+      <c r="AN59" s="106"/>
+      <c r="AO59" s="106"/>
+      <c r="AP59" s="106"/>
+      <c r="AQ59" s="106"/>
+      <c r="AR59" s="106"/>
+      <c r="AS59" s="106"/>
+      <c r="AT59" s="106"/>
+      <c r="AU59" s="106"/>
+      <c r="AV59" s="106"/>
+      <c r="AW59" s="106"/>
+      <c r="AX59" s="106"/>
+      <c r="AY59" s="106"/>
+      <c r="AZ59" s="106"/>
+      <c r="BA59" s="106"/>
+      <c r="BB59" s="106"/>
+      <c r="BC59" s="106"/>
+      <c r="BD59" s="106"/>
+      <c r="BE59" s="106"/>
+      <c r="BF59" s="106"/>
+      <c r="BG59" s="106"/>
+      <c r="BH59" s="107"/>
+      <c r="BI59" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ59" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK59" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL59" s="10">
+        <v>0</v>
+      </c>
+      <c r="BM59" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN59" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO59" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP59" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR59" s="7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="60" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B60" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="E60" s="108"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="109"/>
+      <c r="L60" s="109"/>
+      <c r="M60" s="109"/>
+      <c r="N60" s="109"/>
+      <c r="O60" s="109"/>
+      <c r="P60" s="109"/>
+      <c r="Q60" s="109"/>
+      <c r="R60" s="109"/>
+      <c r="S60" s="109"/>
+      <c r="T60" s="109"/>
+      <c r="U60" s="109"/>
+      <c r="V60" s="109"/>
+      <c r="W60" s="109"/>
+      <c r="X60" s="109"/>
+      <c r="Y60" s="109"/>
+      <c r="Z60" s="109"/>
+      <c r="AA60" s="109"/>
+      <c r="AB60" s="109"/>
+      <c r="AC60" s="109"/>
+      <c r="AD60" s="109"/>
+      <c r="AE60" s="109"/>
+      <c r="AF60" s="109"/>
+      <c r="AG60" s="109"/>
+      <c r="AH60" s="109"/>
+      <c r="AI60" s="109"/>
+      <c r="AJ60" s="109"/>
+      <c r="AK60" s="109"/>
+      <c r="AL60" s="109"/>
+      <c r="AM60" s="109"/>
+      <c r="AN60" s="109"/>
+      <c r="AO60" s="109"/>
+      <c r="AP60" s="109"/>
+      <c r="AQ60" s="109"/>
+      <c r="AR60" s="109"/>
+      <c r="AS60" s="109"/>
+      <c r="AT60" s="109"/>
+      <c r="AU60" s="109"/>
+      <c r="AV60" s="109"/>
+      <c r="AW60" s="109"/>
+      <c r="AX60" s="109"/>
+      <c r="AY60" s="109"/>
+      <c r="AZ60" s="109"/>
+      <c r="BA60" s="109"/>
+      <c r="BB60" s="109"/>
+      <c r="BC60" s="109"/>
+      <c r="BD60" s="109"/>
+      <c r="BE60" s="109"/>
+      <c r="BF60" s="109"/>
+      <c r="BG60" s="109"/>
+      <c r="BH60" s="110"/>
+      <c r="BI60" s="97">
+        <v>1</v>
+      </c>
+      <c r="BJ60" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK60" s="10">
+        <v>1</v>
+      </c>
+      <c r="BL60" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM60" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN60" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO60" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP60" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR60" s="7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="61" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B61" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="BM61" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN61" s="10">
+        <v>0</v>
+      </c>
+      <c r="BO61" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP61" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR61" s="7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="62" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B62" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="BM62" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN62" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO62" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP62" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR62" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="63" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B63" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="P63" s="93"/>
+      <c r="BM63" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN63" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO63" s="10">
+        <v>0</v>
+      </c>
+      <c r="BP63" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR63" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="64" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B64" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="BM64" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN64" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO64" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP64" s="10">
+        <v>0</v>
+      </c>
+      <c r="BR64" s="7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="65" spans="2:70" x14ac:dyDescent="0.2">
+      <c r="B65" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="BM65" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN65" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO65" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP65" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR65" s="7" t="s">
+        <v>227</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="E48:BH60"/>
+    <mergeCell ref="E18:BL18"/>
+    <mergeCell ref="E40:BH46"/>
+    <mergeCell ref="BN5:BP5"/>
+    <mergeCell ref="E8:BL8"/>
+    <mergeCell ref="E47:BL47"/>
+    <mergeCell ref="E9:AJ9"/>
+    <mergeCell ref="AC10:BH10"/>
+    <mergeCell ref="BM4:BP4"/>
+    <mergeCell ref="BI3:BP3"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42B421B1-1094-164B-9C84-07E6F8D5CAEA}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:P83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1889,20 +6616,20 @@
     <col min="2" max="2" width="4" style="7" customWidth="1"/>
     <col min="3" max="3" width="26.6640625" style="7" customWidth="1"/>
     <col min="4" max="4" width="41" style="14" customWidth="1"/>
-    <col min="5" max="5" width="45.5" style="62" customWidth="1"/>
+    <col min="5" max="5" width="45.5" style="61" customWidth="1"/>
     <col min="6" max="16" width="10.83203125" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="55" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="56"/>
+      <c r="A2" s="55"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="56"/>
+      <c r="A3" s="55"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B4" s="7" t="s">
@@ -1912,23 +6639,26 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="56"/>
+    <row r="5" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A5" s="55"/>
       <c r="B5" s="7" t="s">
         <v>56</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>69</v>
       </c>
+      <c r="E5" s="61" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="56"/>
+      <c r="A6" s="55"/>
       <c r="C6" s="7" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="56"/>
+      <c r="A7" s="55"/>
       <c r="B7" s="7" t="s">
         <v>57</v>
       </c>
@@ -1937,22 +6667,25 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="56"/>
+      <c r="A8" s="55"/>
       <c r="C8" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="56"/>
+    <row r="9" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A9" s="55"/>
       <c r="B9" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>1</v>
       </c>
+      <c r="E9" s="61" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="56"/>
+      <c r="A10" s="55"/>
       <c r="C10" s="7" t="s">
         <v>64</v>
       </c>
@@ -1961,7 +6694,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="56"/>
+      <c r="A11" s="55"/>
       <c r="B11" s="7" t="s">
         <v>58</v>
       </c>
@@ -1970,13 +6703,13 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="56"/>
+      <c r="A12" s="55"/>
       <c r="C12" s="7" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="56"/>
+      <c r="A13" s="55"/>
       <c r="B13" s="7" t="s">
         <v>5</v>
       </c>
@@ -1985,14 +6718,14 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="56"/>
+      <c r="A14" s="55"/>
       <c r="C14" s="7" t="s">
         <v>64</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="62" t="s">
+      <c r="E14" s="61" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2004,13 +6737,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="56"/>
+    <row r="16" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A16" s="55"/>
       <c r="B16" s="7" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>3</v>
+      </c>
+      <c r="E16" s="61" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -2019,19 +6755,19 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A18" s="56"/>
+      <c r="A18" s="55"/>
       <c r="B18" s="7" t="s">
         <v>59</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="E18" s="62" t="s">
+      <c r="E18" s="61" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="56"/>
+      <c r="A19" s="55"/>
       <c r="C19" s="7" t="s">
         <v>64</v>
       </c>
@@ -2040,19 +6776,19 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A20" s="56"/>
+      <c r="A20" s="55"/>
       <c r="B20" s="7" t="s">
         <v>62</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="62" t="s">
+      <c r="E20" s="61" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="56"/>
+      <c r="A21" s="55"/>
       <c r="C21" s="7" t="s">
         <v>64</v>
       </c>
@@ -2067,7 +6803,7 @@
       <c r="D23" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="62" t="s">
+      <c r="E23" s="61" t="s">
         <v>89</v>
       </c>
     </row>
@@ -2086,7 +6822,7 @@
       <c r="D25" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="63"/>
+      <c r="E25" s="62"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C26" s="7" t="s">
@@ -2103,7 +6839,7 @@
       <c r="D27" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E27" s="62" t="s">
+      <c r="E27" s="61" t="s">
         <v>88</v>
       </c>
     </row>
@@ -2132,7 +6868,7 @@
       <c r="D31" s="14">
         <v>0</v>
       </c>
-      <c r="E31" s="62" t="s">
+      <c r="E31" s="61" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2143,7 +6879,7 @@
       <c r="D32" s="14">
         <v>0</v>
       </c>
-      <c r="E32" s="62" t="s">
+      <c r="E32" s="61" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2154,7 +6890,7 @@
       <c r="D33" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="E33" s="62" t="s">
+      <c r="E33" s="61" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2173,7 +6909,7 @@
       <c r="D37" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E37" s="62" t="s">
+      <c r="E37" s="61" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2184,7 +6920,7 @@
       <c r="D38" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="62" t="s">
+      <c r="E38" s="61" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2195,7 +6931,7 @@
       <c r="D39" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E39" s="62" t="s">
+      <c r="E39" s="61" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2206,7 +6942,7 @@
       <c r="D40" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="E40" s="62" t="s">
+      <c r="E40" s="61" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2242,7 +6978,7 @@
       <c r="D46" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="E46" s="62" t="s">
+      <c r="E46" s="61" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2255,82 +6991,82 @@
       </c>
     </row>
     <row r="50" spans="2:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="C50" s="57" t="s">
+      <c r="C50" s="56" t="s">
         <v>46</v>
       </c>
       <c r="D50" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E50" s="62" t="s">
+      <c r="E50" s="61" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="51" spans="2:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="C51" s="57" t="s">
+      <c r="C51" s="56" t="s">
         <v>47</v>
       </c>
       <c r="D51" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E51" s="62" t="s">
+      <c r="E51" s="61" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="52" spans="2:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="C52" s="57" t="s">
+      <c r="C52" s="56" t="s">
         <v>48</v>
       </c>
       <c r="D52" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E52" s="62" t="s">
+      <c r="E52" s="61" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="53" spans="2:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="C53" s="57" t="s">
+      <c r="C53" s="56" t="s">
         <v>49</v>
       </c>
       <c r="D53" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E53" s="62" t="s">
+      <c r="E53" s="61" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C54" s="57" t="s">
+      <c r="C54" s="56" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C55" s="57" t="s">
+      <c r="C55" s="56" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C56" s="57" t="s">
+      <c r="C56" s="56" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C57" s="57" t="s">
+      <c r="C57" s="56" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C58" s="57" t="s">
+      <c r="C58" s="56" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="59" spans="2:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="C59" s="57" t="s">
+      <c r="C59" s="56" t="s">
         <v>82</v>
       </c>
       <c r="D59" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E59" s="62" t="s">
+      <c r="E59" s="61" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2343,40 +7079,40 @@
       </c>
     </row>
     <row r="63" spans="2:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="C63" s="57" t="s">
+      <c r="C63" s="56" t="s">
         <v>46</v>
       </c>
       <c r="D63" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E63" s="62" t="s">
+      <c r="E63" s="61" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="64" spans="2:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="C64" s="57" t="s">
+      <c r="C64" s="56" t="s">
         <v>47</v>
       </c>
       <c r="D64" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E64" s="62" t="s">
+      <c r="E64" s="61" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="65" spans="2:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="C65" s="57" t="s">
+      <c r="C65" s="56" t="s">
         <v>48</v>
       </c>
       <c r="D65" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="E65" s="62" t="s">
+      <c r="E65" s="61" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C66" s="57" t="s">
+      <c r="C66" s="56" t="s">
         <v>49</v>
       </c>
       <c r="D66" s="14" t="s">
@@ -2384,51 +7120,51 @@
       </c>
     </row>
     <row r="67" spans="2:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="C67" s="57" t="s">
+      <c r="C67" s="56" t="s">
         <v>50</v>
       </c>
       <c r="D67" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E67" s="62" t="s">
+      <c r="E67" s="61" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="68" spans="2:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="C68" s="57" t="s">
+      <c r="C68" s="56" t="s">
         <v>51</v>
       </c>
       <c r="D68" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E68" s="62" t="s">
+      <c r="E68" s="61" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C69" s="57" t="s">
+      <c r="C69" s="56" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="70" spans="2:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="C70" s="57" t="s">
+      <c r="C70" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="D70" s="58" t="s">
+      <c r="D70" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="E70" s="62" t="s">
+      <c r="E70" s="61" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="71" spans="2:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="C71" s="57" t="s">
+      <c r="C71" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="D71" s="58" t="s">
+      <c r="D71" s="57" t="s">
         <v>80</v>
       </c>
-      <c r="E71" s="62" t="s">
+      <c r="E71" s="61" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2441,7 +7177,7 @@
       </c>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C75" s="57" t="s">
+      <c r="C75" s="56" t="s">
         <v>46</v>
       </c>
       <c r="D75" s="14" t="s">
@@ -2449,7 +7185,7 @@
       </c>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C76" s="57" t="s">
+      <c r="C76" s="56" t="s">
         <v>47</v>
       </c>
       <c r="D76" s="14" t="s">
@@ -2457,54 +7193,54 @@
       </c>
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C77" s="57" t="s">
+      <c r="C77" s="56" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C78" s="57" t="s">
+      <c r="C78" s="56" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="79" spans="2:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="C79" s="57" t="s">
+      <c r="C79" s="56" t="s">
         <v>50</v>
       </c>
       <c r="D79" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E79" s="62" t="s">
+      <c r="E79" s="61" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="80" spans="2:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="C80" s="57" t="s">
+      <c r="C80" s="56" t="s">
         <v>51</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E80" s="62" t="s">
+      <c r="E80" s="61" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C81" s="57" t="s">
+      <c r="C81" s="56" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C82" s="57" t="s">
+      <c r="C82" s="56" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="83" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C83" s="57" t="s">
+      <c r="C83" s="56" t="s">
         <v>54</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup scale="66" fitToHeight="2" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>